--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인플레이션나우캐스트" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="나우캐스트(일별)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실적치(FRED,2000~)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -454,42 +455,42 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>CPI MoM(%)</t>
+          <t>CPI MoM나우캐스트(%)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>CPI YoY(%)</t>
+          <t>CPI YoY나우캐스트(%)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>CoreCPI MoM(%)</t>
+          <t>CoreCPI MoM나우캐스트(%)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CoreCPI YoY(%)</t>
+          <t>CoreCPI YoY나우캐스트(%)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>PCE MoM(%)</t>
+          <t>PCE MoM나우캐스트(%)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>PCE YoY(%)</t>
+          <t>PCE YoY나우캐스트(%)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>CorePCE MoM(%)</t>
+          <t>CorePCE MoM나우캐스트(%)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>CorePCE YoY(%)</t>
+          <t>CorePCE YoY나우캐스트(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -578,6 +579,9587 @@
         <is>
           <t>09/04</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I308"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>CPI YoY실적(%)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>CPI MoM실적(%)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>CoreCPI YoY실적(%)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>CoreCPI MoM실적(%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>PCE YoY실적(%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>PCE MoM실적(%)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>CorePCE YoY실적(%)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CorePCE MoM실적(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2001-01-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.721204961606595</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.572737686139746</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.565532626882328</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3273322422258529</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.701443236797751</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.4841023990559412</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.005221651010691</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.3721115010262954</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2001-02-01</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.529411764705892</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.2277904328018332</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.787068004459314</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.2718868950516651</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.537197196376595</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1548070250360301</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.035879862930856</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1767903319436437</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2001-03-01</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.982456140350864</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.05681818181817455</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.611111111111097</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1626898047722314</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.108700088429383</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.009327363820488266</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.932464327861827</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1040431976820688</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2001-04-01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.218256290228205</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.1703577512776944</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.66222961730449</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2165674066053169</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.373236751810892</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.175871027912855</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.027688060361577</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1591916746700894</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2001-05-01</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.563084112149539</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5102040816326481</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.54565578306587</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1080497028633332</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.557649139514329</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2633433971298338</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.94251442494342</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.02364376724024453</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2001-06-01</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.193960511033689</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.2256063169768563</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.705687465488693</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.3777657852131577</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.391734685576363</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.1764276712873825</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.092195735345248</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.223249461574837</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2001-07-01</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.72148233931675</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.1688238604389269</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.699724517906343</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.2150537634408645</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.101732509230581</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.03310469027252294</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.122122122122128</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.2581304541523721</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2001-08-01</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.72148233931675</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.638812534359536</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1609442060085842</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.096464414207255</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.01192163511848365</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.042094880100231</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0496634646801164</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2001-09-01</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.592165898617504</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.3945885005636862</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.633022490400427</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.2142474558114671</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.31309594354363</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.3404695034709193</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.216706780314603</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.568233772680371</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2001-10-01</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.127659574468077</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.2807411566535634</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.628696604600234</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1603420630678754</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.531881699460702</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.3522671381285924</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.787326711637527</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.7041698415617859</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2001-11-01</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.894374282433997</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.05630630630630851</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.730748225013646</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.3735325506937004</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.321568153430852</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.06755682721347744</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.814663114221715</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.2035118845722383</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2001-12-01</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.603665521191311</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.05633802816901179</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.782324058919805</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1594896331738482</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.062075069396951</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.1033920547182654</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.738727405151308</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.02343444863950328</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2002-01-01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.195899772209574</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.1691093573844338</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.610114192495905</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.1592356687897922</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.6659371163187933</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.09022995369079023</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.418280648055292</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.05596917790386957</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2002-02-01</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.136363636363646</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.1688238604389491</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.548806941431669</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.2119766825649183</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.679565078349853</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.1683657912529446</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.432898722507558</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1912294623460209</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2002-03-01</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.362862010221466</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.2808988764045006</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.436383324309688</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.05288207297726721</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9433082406235416</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.271314751581575</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.448512676130465</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1194525954971493</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2002-04-01</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.643990929705219</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.4481792717086819</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.485143165856285</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.264270613107831</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.187705321398647</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.4184100418409997</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.56968343622752</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2788224614187484</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2002-05-01</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.240834743372798</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.1115448968209698</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.536427415002684</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.1581444385872599</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.9882602639782245</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.06572029442690752</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.658612176288288</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.1112188813449766</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2002-06-01</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.069217782779974</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.05571030640667551</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.258064516129021</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.1052631578947416</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.9362006409068035</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.1247865493235301</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.593333158625754</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.1588921471108895</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2002-07-01</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.465614430665152</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.222717149220486</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.199570815450635</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.1577287066246047</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.192163511848787</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.2204001311905568</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.538260471802899</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2037815667964793</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2002-08-01</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.747463359639223</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.2777777777777768</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.356722013926094</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.314960629921246</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.402946319749887</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.1963530689984783</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.687719619087424</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.1969314729959315</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2002-09-01</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.516002245929271</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.1662049861495873</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.244788882950299</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.1046572475144059</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.932816674864068</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.1802908169264317</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.43569195196931</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.1631447106429373</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2002-10-01</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2.027027027027017</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.221238938053081</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2.187833511205972</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.1045478306325176</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.760451438563027</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.1825745621470753</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.805515693897264</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.08464577027651465</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2002-11-01</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2.25352112676056</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.1655629139072801</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.020202020202033</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.2088772845953102</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.929985021407465</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.09893128181097666</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.697695612550443</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.09738845177991173</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2002-12-01</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2.480270574971821</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.1652892561983643</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.963906581740971</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.1042209484106271</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.13367302257077</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.09623262285913814</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.768886343520593</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.09345315820465938</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2003-01-01</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2.757456387169399</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.4400440044004306</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.960784313725505</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.1561686621551317</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.34651535840702</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.2988138389782957</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.780905673140709</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.06778620486780351</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2003-02-01</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>3.146067415730336</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.5476451259583737</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.797990481226863</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.05197505197505059</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.604621615183023</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.4209790028626648</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.726869043600199</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.1380368098159668</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2003-03-01</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>3.025210084033625</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.1633986928104569</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.744186046511631</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.589654580732015</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.2566880788380743</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.768901569186876</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.1608209526726911</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2003-04-01</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2.175125488008911</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.3806416530723333</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.476014760147604</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.988696109358568</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.1698295271791439</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.598448108632411</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.1108647450110967</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2003-05-01</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1.894150417827301</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.1637554585152801</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.526315789473687</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.2077922077922123</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.80480756600554</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-0.1147010683953398</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.63155107155315</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.1438372729471338</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2003-06-01</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1.948775055679297</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.1093493712411187</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.472134595162999</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.05184033177811909</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.788127254837657</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.1083815028901647</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.527071994221885</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.05592698985688038</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2003-07-01</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2.055555555555544</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.3276897870016393</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.522309711286085</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.2072538860103723</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.862736114565466</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.2938598752384447</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.574164650157051</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.2502604232831107</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2003-08-01</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2.216066481994461</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.4354926510615087</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.308215593929885</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.1034126163391935</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.0067151797029</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.3379767657037069</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.488856060119481</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.1127795729582548</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2003-09-01</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2.378318584070782</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.3252032520325132</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.254573967590167</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.05165289256197081</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.141338793182146</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.3125040023565839</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.464628328117801</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.1392334565338382</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2003-10-01</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2.041942604856528</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.1080497028633109</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.305483028720622</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.1548786783686085</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.968211817081267</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.01276764168891553</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.565903790461065</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.1845438228379237</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2003-11-01</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1.928374655647391</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.05408328826392861</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.094319958311618</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.996176703902619</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.1263835165256078</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.6053460327214</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.136260408781208</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2003-12-01</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2.035203520352025</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.2702702702702675</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1.0931806350859</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.1030927835051543</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.122877447350291</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.2205732354141121</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.637100796807656</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.1247354097369202</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2.026286966046009</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.4312668463611891</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1.143451143451135</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.2059732234809486</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.212406575044379</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.3867438458113437</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.828987730061371</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.2567103325908926</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2004-02-01</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1.688453159041381</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.2147074610842514</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.246753246753252</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.1541623843782203</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.000619147124838</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.2129034710869337</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.853270026037679</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.1619158790525876</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2004-03-01</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1.740076128330603</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.2142474558114671</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.558441558441559</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.307850179579261</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.896429720167259</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.1542800055641891</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.860488824323969</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.1679197994987502</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2004-04-01</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2.292576419213987</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.1603420630678754</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1.766233766233771</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.2046035805626678</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.259224414573469</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.18560840414652</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.012448925039134</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.2602146771086167</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2004-05-01</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2.897758337889544</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.4268943436499306</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.710730948678063</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.153139356814691</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.709537572254317</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.3251581680235871</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2.005745227139832</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.1372563699433504</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2004-06-01</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>3.167667941015839</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.3719447396386855</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.865284974093262</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.2038735983690199</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.890910965613247</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.2851615496708648</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2.110063771945425</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.1582515077505953</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2004-07-01</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2.939575394665228</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.1058761249338236</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1.75801447776629</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.1017293997965574</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2.684537884239746</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.09269581991957487</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.975543306088823</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.11819007452194</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2004-08-01</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2.547425474254728</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.05288207297726721</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1.704545454545459</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.0508130081300795</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2.391167919671111</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.05131093173142975</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.899903802339109</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.03852175858038986</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2004-09-01</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2.539168017287952</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.3171247357294016</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1.961796592669085</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.3047232097511454</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2.273916984793756</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.1976334025467263</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.94908612887732</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.1875659896900972</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2004-10-01</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>3.190914007571655</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.5268703898840821</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2.010309278350508</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.2025316455696258</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2.700011489410592</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.4294417257565186</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1.982084279586172</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.2169708391192238</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2004-11-01</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>3.621621621621607</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.4716981132075304</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2.216494845360839</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.2021222839818204</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2.965626274989797</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.3853420843277666</v>
+      </c>
+      <c r="H48" t="n">
+        <v>2.062544098377184</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.2152639457633665</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>3.342318059299187</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.265705458290435</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.1512859304084735</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2.793715412505571</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.05324549889795804</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2.066266500559966</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.1283871365965084</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2.844873859366603</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.05216484089722861</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2.261048304213764</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.2014098690835908</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.53203056685547</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.1311864952166397</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2.171430005899255</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.3600093701068952</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2005-02-01</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>3.053026245313339</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.4175365344467608</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2.308876346844535</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.2010050251256335</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2.598732880610055</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.2780970744187927</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2.17543859649123</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.1658456284320931</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2005-03-01</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>3.206841261357574</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.3638253638253541</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2.35294117647058</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.3510531594784316</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2.747509438250484</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.299511906522687</v>
+      </c>
+      <c r="H52" t="n">
+        <v>2.255610878975145</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.246516875981162</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2005-04-01</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>3.361792956243326</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.3107198342827466</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2.194997447677371</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.04997501249375258</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2.844503818718014</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.2801843317972175</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2.107509171221089</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.1150029974185562</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2005-05-01</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>2.869287991498415</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.05162622612286949</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2.191641182466886</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.1498501498501614</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2.568966383598825</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.05637047657562899</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2.176892787718687</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.2053011694834295</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2005-06-01</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2.541026998411855</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.05165289256197081</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2.034587995930814</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.04987531172069293</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2.341195776076965</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.06246249188599506</v>
+      </c>
+      <c r="H55" t="n">
+        <v>2.086365841824356</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.06951304284199544</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2005-07-01</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>3.067160232681121</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.6195147134744561</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2.083333333333326</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.1495513459621289</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2.679431825292533</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.4235006119950979</v>
+      </c>
+      <c r="H56" t="n">
+        <v>2.114968809801931</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.1462415911085202</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2005-08-01</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3.646934460887952</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.6157003591585442</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2.133062468257996</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.09955201592830587</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3.040802541715659</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.4034322209492069</v>
+      </c>
+      <c r="H57" t="n">
+        <v>2.158872119744104</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.08153232087226847</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2005-09-01</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>4.741833508956805</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1.37684854665987</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.924050632911389</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.09945300845350946</v>
+      </c>
+      <c r="F58" t="n">
+        <v>3.830020972735437</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.9650752030299747</v>
+      </c>
+      <c r="H58" t="n">
+        <v>2.193265225153729</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.2212954293982383</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2005-10-01</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>4.350104821802936</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.1509054325955717</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2.071753410813537</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.3477396920019915</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3.551362370723954</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.1599095849564858</v>
+      </c>
+      <c r="H59" t="n">
+        <v>2.26522002696985</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.2875341219290339</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2005-11-01</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>3.338549817423053</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.5022601707684538</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2.118003025718607</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.2475247524752477</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2.938408578716656</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-0.2088710161454954</v>
+      </c>
+      <c r="H60" t="n">
+        <v>2.306030491944955</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.2552563451162504</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2005-12-01</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>3.338549817423053</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2.114803625377659</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.1481481481481639</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2.883627677875267</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>2.280881283211489</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.1037732433965211</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>4.018789144050117</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.6057546693589266</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2.110552763819085</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.1972386587770991</v>
+      </c>
+      <c r="F62" t="n">
+        <v>3.246937842213904</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.4847770386498418</v>
+      </c>
+      <c r="H62" t="n">
+        <v>2.142479822115217</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.2242071384659816</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2006-02-01</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>3.63825363825363</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.05017561465128217</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2.106318956870612</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.1968503937007871</v>
+      </c>
+      <c r="F63" t="n">
+        <v>3.022235369521264</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.05985586707208945</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2.137706043956045</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.1611642311624362</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2006-03-01</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>3.417918177110302</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.1504513540621755</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2.098950524737631</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.3438113948919463</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2.913671274961582</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.1938169984685878</v>
+      </c>
+      <c r="H64" t="n">
+        <v>2.167928844953937</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.276180069405263</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2006-04-01</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>3.613835828600931</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.5007511266900355</v>
+      </c>
+      <c r="D65" t="n">
+        <v>2.29770229770232</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.2447381302006946</v>
+      </c>
+      <c r="F65" t="n">
+        <v>3.102827101944805</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.4644997970052467</v>
+      </c>
+      <c r="H65" t="n">
+        <v>2.362185479830381</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.3053563089008282</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2006-05-01</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>3.977272727272729</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.2989536621823774</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2.44389027431422</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.29296875</v>
+      </c>
+      <c r="F66" t="n">
+        <v>3.321534862643749</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.2686159148986844</v>
+      </c>
+      <c r="H66" t="n">
+        <v>2.408565958121445</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.2507043598682035</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2006-06-01</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>4.181724315952517</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.24838549428714</v>
+      </c>
+      <c r="D67" t="n">
+        <v>2.642073778664011</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.2434274586173402</v>
+      </c>
+      <c r="F67" t="n">
+        <v>3.511627906976744</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.2465594291200857</v>
+      </c>
+      <c r="H67" t="n">
+        <v>2.595788242176078</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.2524590944816385</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2006-07-01</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>4.104669061056954</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.5450941526263575</v>
+      </c>
+      <c r="D68" t="n">
+        <v>2.687904430064703</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.1942690626517862</v>
+      </c>
+      <c r="F68" t="n">
+        <v>3.427345635375278</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.3417327862455632</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2.545755451713405</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.09740336873114153</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2006-08-01</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>3.926568077511483</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.4435682602267121</v>
+      </c>
+      <c r="D69" t="n">
+        <v>2.83441074092492</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.2423654871546388</v>
+      </c>
+      <c r="F69" t="n">
+        <v>3.335882588586636</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.3146432864314486</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2.671351969164548</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.2041106944510318</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2006-09-01</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>2.012072434607637</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.4906771344455385</v>
+      </c>
+      <c r="D70" t="n">
+        <v>2.930948832588176</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.19342359767891</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2.080026932140622</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-0.2619676945668115</v>
+      </c>
+      <c r="H70" t="n">
+        <v>2.606005459508642</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.1575082899099911</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2006-10-01</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1.406328478151697</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.4437869822485285</v>
+      </c>
+      <c r="D71" t="n">
+        <v>2.772277227722775</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.1930501930502038</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1.67697016985775</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-0.2355657110550968</v>
+      </c>
+      <c r="H71" t="n">
+        <v>2.496915148435797</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.1809088006810677</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2006-11-01</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1.968702675416467</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.04952947003467045</v>
+      </c>
+      <c r="D72" t="n">
+        <v>2.617283950617288</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.09633911368016612</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1.924673106302088</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.0342376803381228</v>
+      </c>
+      <c r="H72" t="n">
+        <v>2.284218020344375</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.04721100960745073</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2006-12-01</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>2.523977788995446</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.544554455445545</v>
+      </c>
+      <c r="D73" t="n">
+        <v>2.61341222879683</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.1443695861405025</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2.286752234425182</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.3552418831360482</v>
+      </c>
+      <c r="H73" t="n">
+        <v>2.31560168275895</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.1344878842932218</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2007-01-01</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>2.075765178123423</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.1659281142294633</v>
+      </c>
+      <c r="D74" t="n">
+        <v>2.657480314960625</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.2402691013935643</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2.133263102449301</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.3339919089284216</v>
+      </c>
+      <c r="H74" t="n">
+        <v>2.500451019303629</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.4052780395852995</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2007-02-01</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>2.420260782347028</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.3878350545869269</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2.71856581532417</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.2564717162032659</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.389213246554367</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.3106099676496887</v>
+      </c>
+      <c r="H75" t="n">
+        <v>2.556466816364278</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.2159016239556832</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2007-03-01</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>2.798197295943927</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.5200121434097538</v>
+      </c>
+      <c r="D76" t="n">
+        <v>2.50513950073421</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.1353192913668311</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2.564898622023759</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.3657353851906464</v>
+      </c>
+      <c r="H76" t="n">
+        <v>2.376989306541799</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.1006931434994307</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2007-04-01</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>2.592924763328353</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.3000662483924943</v>
+      </c>
+      <c r="D77" t="n">
+        <v>2.41552734374999</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.1571020638149623</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2.330777916443805</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.2351735860479209</v>
+      </c>
+      <c r="H77" t="n">
+        <v>2.210973687980511</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.1427000725197081</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2007-05-01</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2.709885742672613</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.4132994016629032</v>
+      </c>
+      <c r="D78" t="n">
+        <v>2.267770204479058</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.1482738728086685</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2.352983013477794</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.2903735365173743</v>
+      </c>
+      <c r="H78" t="n">
+        <v>2.075642460761662</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.1179686039992411</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2007-06-01</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>2.692765113974227</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.231675171096235</v>
+      </c>
+      <c r="D79" t="n">
+        <v>2.181641573579407</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.159003703738958</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2.317634121250101</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.211938016816049</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1.987266291307321</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.1656614207216744</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2007-07-01</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>2.317890586495808</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.1780595848171584</v>
+      </c>
+      <c r="D80" t="n">
+        <v>2.168201648085311</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.1810905357618076</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2.12472601286855</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.1525500121346557</v>
+      </c>
+      <c r="H80" t="n">
+        <v>2.041106944510362</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.150246334105919</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2007-08-01</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1.897448478900876</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.03082807088530259</v>
+      </c>
+      <c r="D81" t="n">
+        <v>2.088491295938089</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.1641576482756424</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1.873715124816444</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.06808137455140972</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1.984841307437235</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.1488579801832923</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2007-09-01</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>2.833826429980268</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0.4237553390765036</v>
+      </c>
+      <c r="D82" t="n">
+        <v>2.101351351351366</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.2060449320051783</v>
+      </c>
+      <c r="F82" t="n">
+        <v>2.534687050952855</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.3851476014760102</v>
+      </c>
+      <c r="H82" t="n">
+        <v>2.102325801378702</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.2728877328254997</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2007-10-01</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>3.610698365527476</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0.3083237831280172</v>
+      </c>
+      <c r="D83" t="n">
+        <v>2.15655105973025</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.2472182043355309</v>
+      </c>
+      <c r="F83" t="n">
+        <v>3.08847488843238</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.3032600454889955</v>
+      </c>
+      <c r="H83" t="n">
+        <v>2.183509194344113</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.2605644404812812</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2007-11-01</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>4.373267326732666</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.7858884267890387</v>
+      </c>
+      <c r="D84" t="n">
+        <v>2.338787295476408</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.2749001541892726</v>
+      </c>
+      <c r="F84" t="n">
+        <v>3.599627055033006</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.53024576834102</v>
+      </c>
+      <c r="H84" t="n">
+        <v>2.33584220088241</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.1963592681574644</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2007-12-01</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>4.108813392417532</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0.2898014551732553</v>
+      </c>
+      <c r="D85" t="n">
+        <v>2.435367611725137</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.2388789617229437</v>
+      </c>
+      <c r="F85" t="n">
+        <v>3.471634208298058</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.231257333591528</v>
+      </c>
+      <c r="H85" t="n">
+        <v>2.403393025447698</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.2005856177806464</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2008-01-01</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>4.294695655165981</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.3447705076970342</v>
+      </c>
+      <c r="D86" t="n">
+        <v>2.47890699904123</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.2828754784958143</v>
+      </c>
+      <c r="F86" t="n">
+        <v>3.387406817009708</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.2523186033824398</v>
+      </c>
+      <c r="H86" t="n">
+        <v>2.193044212897766</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.1990335941095323</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2008-02-01</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>4.142959270611968</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.2417826877939788</v>
+      </c>
+      <c r="D87" t="n">
+        <v>2.29708083295479</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.07858877022608457</v>
+      </c>
+      <c r="F87" t="n">
+        <v>3.272922728175653</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.1995329115933142</v>
+      </c>
+      <c r="H87" t="n">
+        <v>2.072405395279131</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.09759682178820395</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2008-03-01</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>3.974903550134434</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0.3578027806118822</v>
+      </c>
+      <c r="D88" t="n">
+        <v>2.388524386633417</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.2248304423223324</v>
+      </c>
+      <c r="F88" t="n">
+        <v>3.191142571075978</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.2862573827249859</v>
+      </c>
+      <c r="H88" t="n">
+        <v>2.169742905934924</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.1961504049186713</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2008-04-01</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>3.903760975988813</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.2314381020201539</v>
+      </c>
+      <c r="D89" t="n">
+        <v>2.294669292051843</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.06529241675217179</v>
+      </c>
+      <c r="F89" t="n">
+        <v>3.13951867682587</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.1850284876177666</v>
+      </c>
+      <c r="H89" t="n">
+        <v>2.08372266866006</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.05838647265568042</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2008-05-01</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>4.088413823123993</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0.5917491656617146</v>
+      </c>
+      <c r="D90" t="n">
+        <v>2.322215768978109</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.1752423564504113</v>
+      </c>
+      <c r="F90" t="n">
+        <v>3.282143932550441</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.4290588857982724</v>
+      </c>
+      <c r="H90" t="n">
+        <v>2.148931950488242</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.1819221967963358</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2008-06-01</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>4.935966105947864</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1.04782350098509</v>
+      </c>
+      <c r="D91" t="n">
+        <v>2.3917259211377</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.2270443294748237</v>
+      </c>
+      <c r="F91" t="n">
+        <v>3.811438939546274</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.7254989908050957</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2.214095202599631</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.2295594970248782</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2008-07-01</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>5.497512078341837</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0.7141444751521009</v>
+      </c>
+      <c r="D92" t="n">
+        <v>2.463313612274831</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.2511326500297173</v>
+      </c>
+      <c r="F92" t="n">
+        <v>4.135655023597695</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.4653389292751609</v>
+      </c>
+      <c r="H92" t="n">
+        <v>2.244499232451047</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.1800364630811346</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2008-08-01</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>5.308017162091239</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.1488475727800642</v>
+      </c>
+      <c r="D93" t="n">
+        <v>2.498117175621339</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.1981802606903837</v>
+      </c>
+      <c r="F93" t="n">
+        <v>3.980627306273066</v>
+      </c>
+      <c r="G93" t="n">
+        <v>-0.08089090808356403</v>
+      </c>
+      <c r="H93" t="n">
+        <v>2.217938594453983</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.1228417388930536</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2008-09-01</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>4.953319875136075</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0.08550916822900323</v>
+      </c>
+      <c r="D94" t="n">
+        <v>2.438620872212294</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.1478790903587379</v>
+      </c>
+      <c r="F94" t="n">
+        <v>3.667838353206054</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.08317437785565485</v>
+      </c>
+      <c r="H94" t="n">
+        <v>2.043983277553241</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.1022425192556797</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2008-10-01</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>3.731057889956513</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-0.8598436564828615</v>
+      </c>
+      <c r="D95" t="n">
+        <v>2.221362995515785</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.03460798383114749</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2.671843148033615</v>
+      </c>
+      <c r="G95" t="n">
+        <v>-0.6604097643134965</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1.634402143781188</v>
+      </c>
+      <c r="I95" t="n">
+        <v>-0.1418584593036454</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2008-11-01</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1.099917470616685</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-1.770547708472547</v>
+      </c>
+      <c r="D96" t="n">
+        <v>2.015893915169764</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.07334354300052581</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.9250293343662008</v>
+      </c>
+      <c r="G96" t="n">
+        <v>-1.180131844597376</v>
+      </c>
+      <c r="H96" t="n">
+        <v>1.390265833583104</v>
+      </c>
+      <c r="I96" t="n">
+        <v>-0.04432271482310846</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2008-12-01</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>-0.02222800255385904</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-0.8233522399403226</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1.762459656233584</v>
+      </c>
+      <c r="E97" t="n">
+        <v>-0.01014072561500434</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.1295690125477478</v>
+      </c>
+      <c r="G97" t="n">
+        <v>-0.55873488876097</v>
+      </c>
+      <c r="H97" t="n">
+        <v>1.137827887712839</v>
+      </c>
+      <c r="I97" t="n">
+        <v>-0.04889030380206272</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>-0.1135860190221272</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0.2530771341261451</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1.672350318799087</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.1940762936498697</v>
+      </c>
+      <c r="F98" t="n">
+        <v>-0.1111035530462767</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.01135099548230656</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.9059281457752144</v>
+      </c>
+      <c r="I98" t="n">
+        <v>-0.03071357881445635</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2009-02-01</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>0.008463140671510772</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.3642660652187324</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1.800980653363804</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.2052027642560628</v>
+      </c>
+      <c r="F99" t="n">
+        <v>-0.1312484442533512</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.1793253734053701</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.8878386748950362</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.07965226098631817</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2009-03-01</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>-0.4464787676623838</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-0.0987282856538485</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1.787613095793295</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.2116698501322345</v>
+      </c>
+      <c r="F100" t="n">
+        <v>-0.5257516782309568</v>
+      </c>
+      <c r="G100" t="n">
+        <v>-0.1098950898420825</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.762458642915198</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.07162997998908516</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2009-04-01</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>-0.5763244243767063</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0.1007082519588698</v>
+      </c>
+      <c r="D101" t="n">
+        <v>1.93232662192393</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.2075572844359552</v>
+      </c>
+      <c r="F101" t="n">
+        <v>-0.5675739591662121</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.1429073710714768</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.9279176201372863</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.2226893143214115</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2009-05-01</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>-1.015761495855172</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0.1471493918921984</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1.846130941303459</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.0905324956791409</v>
+      </c>
+      <c r="F102" t="n">
+        <v>-0.8892128279883504</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.1041961605980024</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.8223026759099472</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.07708789153280105</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2009-06-01</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>-1.229174618210915</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0.8299612246622345</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1.711972667855011</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.09501882103570836</v>
+      </c>
+      <c r="F103" t="n">
+        <v>-1.018624689681269</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.5939787525314877</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.7201458523245163</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.1280032623840244</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2009-07-01</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>-1.958761003762277</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.02979654546301225</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1.527099298497436</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.06891452773012396</v>
+      </c>
+      <c r="F104" t="n">
+        <v>-1.466009197185447</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.01124707576030115</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.6255829295479742</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.08598063173139714</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2009-08-01</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>-1.483835566326763</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0.3348453377792993</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1.433965054322472</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.1062650789234842</v>
+      </c>
+      <c r="F105" t="n">
+        <v>-1.100119771104102</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.2901419221340129</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.6509440392611365</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.1480761405253883</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2009-09-01</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>-1.377942862886472</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0.1930887233400513</v>
+      </c>
+      <c r="D106" t="n">
+        <v>1.479837388619964</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.1931698071946597</v>
+      </c>
+      <c r="F106" t="n">
+        <v>-1.022748678626439</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.1614711818793246</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.7251804439602383</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.1760742220566769</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2009-10-01</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>-0.2239682942003385</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0.3001931798703783</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1.712733177113113</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.2641869770825922</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.01338523831302396</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.3795172629976307</v>
+      </c>
+      <c r="H107" t="n">
+        <v>1.239899535179734</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.3684299476085728</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1.914587174470928</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0.3348590589767664</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1.714243571010421</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.0748295926095599</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1.460612012235729</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.2498243422593527</v>
+      </c>
+      <c r="H108" t="n">
+        <v>1.373476441695476</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.08755977638581491</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>2.814123123208367</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0.05201763996427466</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1.823671775959435</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.0974323185266357</v>
+      </c>
+      <c r="F109" t="n">
+        <v>2.089718268292118</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.05785041218417941</v>
+      </c>
+      <c r="H109" t="n">
+        <v>1.509515521732707</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.08524001794527614</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>2.621111388976716</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.06487322116246474</v>
+      </c>
+      <c r="D110" t="n">
+        <v>1.51233517064957</v>
+      </c>
+      <c r="E110" t="n">
+        <v>-0.1122776517672341</v>
+      </c>
+      <c r="F110" t="n">
+        <v>2.301720615608116</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.2190373475355445</v>
+      </c>
+      <c r="H110" t="n">
+        <v>1.690903711795344</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.1479223631718041</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2010-02-01</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>2.151336357866529</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-0.09517766497462166</v>
+      </c>
+      <c r="D111" t="n">
+        <v>1.349452688803998</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.04441765284430854</v>
+      </c>
+      <c r="F111" t="n">
+        <v>2.116330183762716</v>
+      </c>
+      <c r="G111" t="n">
+        <v>-0.00221886926421444</v>
+      </c>
+      <c r="H111" t="n">
+        <v>1.698653811169737</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.0872795631545964</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2010-03-01</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>2.286171439327989</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0.03313681361922782</v>
+      </c>
+      <c r="D112" t="n">
+        <v>1.159205142655551</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.02355808653973224</v>
+      </c>
+      <c r="F112" t="n">
+        <v>2.372716033980193</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.1409013246943314</v>
+      </c>
+      <c r="H112" t="n">
+        <v>1.77696983468727</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.1486930662075503</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>2.20677075253044</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.02300405331419064</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.9675088932173947</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.01766440350934317</v>
+      </c>
+      <c r="F113" t="n">
+        <v>2.282122430488709</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.05428701210934417</v>
+      </c>
+      <c r="H113" t="n">
+        <v>1.60297468569679</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0.05135132118019303</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2010-05-01</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>2.003548929218568</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-0.05197720362644098</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0.9401381427474931</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.06339948012425989</v>
+      </c>
+      <c r="F114" t="n">
+        <v>2.20846957131704</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.03211161554643738</v>
+      </c>
+      <c r="H114" t="n">
+        <v>1.636855877388732</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.1104602510460184</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2010-06-01</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1.121560594068627</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-0.04187951585438165</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0.9501989849939774</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.1049954290782917</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1.562218823105987</v>
+      </c>
+      <c r="G115" t="n">
+        <v>-0.04206378197677552</v>
+      </c>
+      <c r="H115" t="n">
+        <v>1.555570639876902</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.04792474700190397</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2010-07-01</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1.340778480482108</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0.186925354168288</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.9577539302116689</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.07640351908280163</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1.637390072198119</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.08527037352852318</v>
+      </c>
+      <c r="H116" t="n">
+        <v>1.470588235294112</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.002227990241410183</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2010-08-01</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1.150177539511255</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.1461363479699607</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.9171009950067255</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.06595501506574397</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.482395155864524</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.1372015313461095</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1.417623223738418</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.09580144593344109</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2010-09-01</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1.118312247233177</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.1615249422961318</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.8143870498363182</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.09119268291581939</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.419551296404098</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.09944531612562368</v>
+      </c>
+      <c r="H118" t="n">
+        <v>1.296828347698731</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.05675811028880151</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2010-10-01</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1.166695148931463</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.348184629481163</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.6027183550187942</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.05367347583113968</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.35841986103522</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.3190127163546386</v>
+      </c>
+      <c r="H119" t="n">
+        <v>1.078781347522528</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.1523813761039383</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2010-11-01</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1.084544776600338</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.25338416234848</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.672056411046551</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.1438038137312247</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.307196813777289</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.1991615409161485</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1.121579183490362</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.1299379185500049</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2010-12-01</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1.437793022217937</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.4016576346828282</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.6618948664665503</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.08732877483130785</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1.477668197333748</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.2262194988030153</v>
+      </c>
+      <c r="H121" t="n">
+        <v>1.056748397507734</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.02107364685004498</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1.700783491502977</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.3243042200370194</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.9835337415527112</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.206887556612978</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1.559865092748747</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.3002147521584897</v>
+      </c>
+      <c r="H122" t="n">
+        <v>1.123444633425841</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.2140187848612252</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2011-02-01</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>2.124898173333145</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.321447463006419</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1.124445592146106</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.1840190661705599</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1.845030732021202</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.2785606606803492</v>
+      </c>
+      <c r="H123" t="n">
+        <v>1.211904389240437</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.1748329128491211</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2011-03-01</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>2.619241510354109</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0.51735482068338</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1.209785173677336</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.1079686218992792</v>
+      </c>
+      <c r="F124" t="n">
+        <v>2.110546083025899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.4019739207163697</v>
+      </c>
+      <c r="H124" t="n">
+        <v>1.214570379218349</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.1513310504805077</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2011-04-01</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>3.077234444786869</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.4694098975099203</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1.315539212578454</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.1221727961907115</v>
+      </c>
+      <c r="F125" t="n">
+        <v>2.488096556306063</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.4242345333420161</v>
+      </c>
+      <c r="H125" t="n">
+        <v>1.394700139470006</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.2294109212833684</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2011-05-01</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>3.4589718808965</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.3181714734507679</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.454096179433573</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.2002440474328182</v>
+      </c>
+      <c r="F126" t="n">
+        <v>2.766247135788524</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.3035967025724506</v>
+      </c>
+      <c r="H126" t="n">
+        <v>1.523561143060936</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.2376891334250342</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2011-06-01</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>3.502318150636041</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1.583677676609674</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.2328537972565936</v>
+      </c>
+      <c r="F127" t="n">
+        <v>2.788451955127846</v>
+      </c>
+      <c r="G127" t="n">
+        <v>-0.02046575755616509</v>
+      </c>
+      <c r="H127" t="n">
+        <v>1.586329051878765</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.1097803295605493</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2011-07-01</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>3.579880976999616</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.2620036831757044</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1.741483445742964</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.2318678041985267</v>
+      </c>
+      <c r="F128" t="n">
+        <v>2.875699838456258</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.1702237688404384</v>
+      </c>
+      <c r="H128" t="n">
+        <v>1.734451759516076</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.1480409250912862</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2011-08-01</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>3.75499603070808</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.3154462166418792</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1.965157171943366</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.2859451731211493</v>
+      </c>
+      <c r="F129" t="n">
+        <v>2.976729796026611</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.2355421233208199</v>
+      </c>
+      <c r="H129" t="n">
+        <v>1.839630515831048</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.1992860740643421</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2011-09-01</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>3.812621692818685</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.2171547858084377</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1.987722756200627</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.113343546059097</v>
+      </c>
+      <c r="F130" t="n">
+        <v>3.019030377958321</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.1405639727027008</v>
+      </c>
+      <c r="H130" t="n">
+        <v>1.850821969612682</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.06775363902609133</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2011-10-01</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>3.522268130664052</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.06752075270193281</v>
+      </c>
+      <c r="D131" t="n">
+        <v>2.107920479646563</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.1715918237380487</v>
+      </c>
+      <c r="F131" t="n">
+        <v>2.693632332390705</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.002143002560872631</v>
+      </c>
+      <c r="H131" t="n">
+        <v>1.744721966171725</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.0480506716173501</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2011-11-01</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>3.451432214581729</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.1847850055126887</v>
+      </c>
+      <c r="D132" t="n">
+        <v>2.138204538395394</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.1735053376069606</v>
+      </c>
+      <c r="F132" t="n">
+        <v>2.699259844940816</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.2046523588595139</v>
+      </c>
+      <c r="H132" t="n">
+        <v>1.827861579414392</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.211758028248954</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2011-12-01</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>3.062066838419386</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.02377084901548088</v>
+      </c>
+      <c r="D133" t="n">
+        <v>2.276662633858506</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.2230067122376056</v>
+      </c>
+      <c r="F133" t="n">
+        <v>2.526624884954187</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.05774165953806865</v>
+      </c>
+      <c r="H133" t="n">
+        <v>1.974960911076851</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.1655629139072801</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2012-01-01</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>3.008766337985502</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.2724196054096684</v>
+      </c>
+      <c r="D134" t="n">
+        <v>2.277348150608383</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.2075592005452931</v>
+      </c>
+      <c r="F134" t="n">
+        <v>2.569312446745764</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.3419753350289767</v>
+      </c>
+      <c r="H134" t="n">
+        <v>2.061479219227191</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.2990430622009654</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2012-02-01</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>2.898178442347388</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.2137446124946152</v>
+      </c>
+      <c r="D135" t="n">
+        <v>2.15982044056573</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.0688968171425719</v>
+      </c>
+      <c r="F135" t="n">
+        <v>2.51315402464134</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.2236564636717953</v>
+      </c>
+      <c r="H135" t="n">
+        <v>2.025847785264556</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.1398601398601373</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2012-03-01</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>2.582875281332098</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.2093470387029228</v>
+      </c>
+      <c r="D136" t="n">
+        <v>2.248337465429118</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.1947078067305874</v>
+      </c>
+      <c r="F136" t="n">
+        <v>2.298027472169784</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.1912777352716111</v>
+      </c>
+      <c r="H136" t="n">
+        <v>2.044845423362407</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.1699796457494296</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2012-04-01</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>2.273163374134857</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.1660788350006825</v>
+      </c>
+      <c r="D137" t="n">
+        <v>2.314427851801515</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.186888890834136</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1.999848741856369</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.1315175427431869</v>
+      </c>
+      <c r="H137" t="n">
+        <v>1.965337001375511</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.151316998303086</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2012-05-01</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1.737942937466075</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-0.2068180132381081</v>
+      </c>
+      <c r="D138" t="n">
+        <v>2.252258280361308</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.1393591227801805</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1.576940476959887</v>
+      </c>
+      <c r="G138" t="n">
+        <v>-0.1122786204558857</v>
+      </c>
+      <c r="H138" t="n">
+        <v>1.826744683887549</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.1014450523952881</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2012-06-01</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1.653870448297634</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.08263631713106845</v>
+      </c>
+      <c r="D139" t="n">
+        <v>2.192285611289857</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.1740655428750904</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1.546019672696319</v>
+      </c>
+      <c r="G139" t="n">
+        <v>-0.05090029903925819</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1.81925847945521</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.1024203546978519</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2012-07-01</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1.417511479846478</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.02888099280600187</v>
+      </c>
+      <c r="D140" t="n">
+        <v>2.109955687378462</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.1511172661275317</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1.410026135495857</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.03607273961847568</v>
+      </c>
+      <c r="H140" t="n">
+        <v>1.773865054858415</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.1033925686591219</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2012-08-01</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1.685934915482123</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.580952797585188</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1.935252499313744</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.1143627429664784</v>
+      </c>
+      <c r="F141" t="n">
+        <v>1.51186746212284</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3362039708128428</v>
+      </c>
+      <c r="H141" t="n">
+        <v>1.63592254229139</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.06347771824499748</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2012-09-01</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1.949716898281961</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.4771266277542319</v>
+      </c>
+      <c r="D142" t="n">
+        <v>2.008243483490912</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.1850299479223105</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.677971005175349</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.3044236562549596</v>
+      </c>
+      <c r="H142" t="n">
+        <v>1.691602053074148</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.1225740551583199</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2012-10-01</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>2.155678059536936</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.2696794580438588</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1.994649148366934</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.1582422537165229</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1.976877497883844</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.2961230016966576</v>
+      </c>
+      <c r="H143" t="n">
+        <v>1.889449210819305</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.2427002008183132</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2012-11-01</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>1.796019703392626</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-0.1679344494426638</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1.952851268626143</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.132453771036789</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1.699101796407176</v>
+      </c>
+      <c r="G144" t="n">
+        <v>-0.06829596318324027</v>
+      </c>
+      <c r="H144" t="n">
+        <v>1.783069013593575</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0.10712946595961</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2012-12-01</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1.759504979689552</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.01210816046771646</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1.899694377872074</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.1707517399386127</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1.624382841387551</v>
+      </c>
+      <c r="G145" t="n">
+        <v>-0.01577137810302442</v>
+      </c>
+      <c r="H145" t="n">
+        <v>1.689865158764681</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0.07384022687142444</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2013-01-01</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>1.684061762098299</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0.1980788942180789</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1.909802217863144</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.2174991908512336</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1.470807506336924</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0.190337981365829</v>
+      </c>
+      <c r="H146" t="n">
+        <v>1.591586707865789</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0.202108775156673</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2013-02-01</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>2.018140490257481</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0.5429926752100966</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1.988738521448563</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.1464072101244884</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1.604607668111879</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0.3558121228024236</v>
+      </c>
+      <c r="H147" t="n">
+        <v>1.560131653024999</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0.1088545724256429</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2013-03-01</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>1.518747241124618</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-0.2811919102589933</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1.889022137798824</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.09674548198599364</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1.276992915022701</v>
+      </c>
+      <c r="G148" t="n">
+        <v>-0.1317798648733493</v>
+      </c>
+      <c r="H148" t="n">
+        <v>1.480744911965948</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0.0916795479985133</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2013-04-01</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>1.138808047576867</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-0.2087979266581219</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1.715558856294086</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.01632344476232284</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1.04122531988815</v>
+      </c>
+      <c r="G149" t="n">
+        <v>-0.1015834450402098</v>
+      </c>
+      <c r="H149" t="n">
+        <v>1.37706262613182</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0.04899298122289508</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2013-05-01</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1.390388827919709</v>
+      </c>
+      <c r="C150" t="n">
+        <v>0.04141554895016331</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1.645551949185076</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0.07043705332601125</v>
+      </c>
+      <c r="F150" t="n">
+        <v>1.229030137218712</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0.07338218490213766</v>
+      </c>
+      <c r="H150" t="n">
+        <v>1.392916823890888</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0.1170997583486821</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2013-06-01</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>1.715793527156872</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0.2380408205508555</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1.623095247427297</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.1519339387800578</v>
+      </c>
+      <c r="F151" t="n">
+        <v>1.505506397606471</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0.2220802212421935</v>
+      </c>
+      <c r="H151" t="n">
+        <v>1.463651050080794</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0.1722542983827235</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2013-07-01</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>1.885471805415806</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0.1957452300544338</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1.700221768056709</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0.2271266338118805</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1.595112845749203</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0.124382009553381</v>
+      </c>
+      <c r="H152" t="n">
+        <v>1.487960751404027</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0.1273763653154125</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>1.538809488600279</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0.2387290682696275</v>
+      </c>
+      <c r="D153" t="n">
+        <v>1.782107690904433</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.1949717804002216</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1.404788330426499</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0.1482378486721281</v>
+      </c>
+      <c r="H153" t="n">
+        <v>1.533250900489214</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0.1081321756829956</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2013-09-01</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>1.0947341081748</v>
+      </c>
+      <c r="C154" t="n">
+        <v>0.03769446919335007</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1.751936841831436</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0.1553325139969752</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1.141285447820173</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0.04378009881793599</v>
+      </c>
+      <c r="H154" t="n">
+        <v>1.529226044094134</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0.1186051190816606</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2013-10-01</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>0.8767991434911471</v>
+      </c>
+      <c r="C155" t="n">
+        <v>0.05352310485391421</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1.686837731144819</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0.09416276097145015</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.9761069199571093</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0.1323247478536294</v>
+      </c>
+      <c r="H155" t="n">
+        <v>1.45481814773154</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0.1692351628359567</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2013-11-01</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>1.232870196195446</v>
+      </c>
+      <c r="C156" t="n">
+        <v>0.184448942735238</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1.741667747373876</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0.1864456561993189</v>
+      </c>
+      <c r="F156" t="n">
+        <v>1.195470460208803</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0.1487986847444889</v>
+      </c>
+      <c r="H156" t="n">
+        <v>1.514259724971923</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0.1657814430376936</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2013-12-01</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>1.51283836675733</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0.2644169158479315</v>
+      </c>
+      <c r="D157" t="n">
+        <v>1.740856618836983</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0.1699531354228956</v>
+      </c>
+      <c r="F157" t="n">
+        <v>1.388100195595943</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0.174552708684006</v>
+      </c>
+      <c r="H157" t="n">
+        <v>1.547361892336974</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0.1064726966055307</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>1.557758795574915</v>
+      </c>
+      <c r="C158" t="n">
+        <v>0.242417529045369</v>
+      </c>
+      <c r="D158" t="n">
+        <v>1.607034435837029</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0.08568071632473195</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1.405405405405413</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0.2074387537079669</v>
+      </c>
+      <c r="H158" t="n">
+        <v>1.452461500698998</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0.1084655806067758</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2014-02-01</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>1.120474634772495</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0.1100778620244158</v>
+      </c>
+      <c r="D159" t="n">
+        <v>1.554807390494872</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0.09493094197770002</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1.093982052837439</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0.04761214730784058</v>
+      </c>
+      <c r="H159" t="n">
+        <v>1.390117797558754</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0.04733653117898751</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2014-03-01</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>1.612694913940804</v>
+      </c>
+      <c r="C160" t="n">
+        <v>0.204205530106516</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1.645660970643559</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0.1862946419120659</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1.38970341823057</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0.1603558866128729</v>
+      </c>
+      <c r="H160" t="n">
+        <v>1.447423075694143</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0.1482509541683719</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>2.015125303606169</v>
+      </c>
+      <c r="C161" t="n">
+        <v>0.1864185605097601</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1.821055525013748</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0.1889064976228205</v>
+      </c>
+      <c r="F161" t="n">
+        <v>1.673113815768779</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0.1776584206992782</v>
+      </c>
+      <c r="H161" t="n">
+        <v>1.571265848387737</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0.1711286089238762</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2014-05-01</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>2.166947687079812</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0.1903005903547195</v>
+      </c>
+      <c r="D162" t="n">
+        <v>1.945526961836253</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0.1927684416548558</v>
+      </c>
+      <c r="F162" t="n">
+        <v>1.766166287803395</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0.1649705630651699</v>
+      </c>
+      <c r="H162" t="n">
+        <v>1.62365625697789</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0.1687401087901996</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2014-06-01</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>2.058981694594419</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0.1321132206079767</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1.922862652667656</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.1296683773349683</v>
+      </c>
+      <c r="F163" t="n">
+        <v>1.651458614238077</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0.1091129937105473</v>
+      </c>
+      <c r="H163" t="n">
+        <v>1.563544884246726</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0.1130014439073346</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2014-07-01</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>1.974237870330597</v>
+      </c>
+      <c r="C164" t="n">
+        <v>0.1125485286492811</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1.844963229006336</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0.1505232575251148</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1.669241690329049</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0.1418979363104533</v>
+      </c>
+      <c r="H164" t="n">
+        <v>1.610321322180885</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0.1734913567860152</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2014-08-01</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>1.715098348296906</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-0.01600013473797013</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1.73639560289498</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.08816305967800364</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1.506243875998092</v>
+      </c>
+      <c r="G165" t="n">
+        <v>-0.01232146707601522</v>
+      </c>
+      <c r="H165" t="n">
+        <v>1.539748599506519</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0.03860278774727721</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2014-09-01</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>1.684050971123208</v>
+      </c>
+      <c r="C166" t="n">
+        <v>0.007159100480080838</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1.740945888368128</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0.1598120844780837</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1.497249312328086</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0.0349151254377178</v>
+      </c>
+      <c r="H166" t="n">
+        <v>1.554848058555369</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0.1334932471189543</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2014-10-01</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>1.609541702151329</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-0.01979139032411981</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1.817632310436279</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0.1696079334634337</v>
+      </c>
+      <c r="F167" t="n">
+        <v>1.332944861242624</v>
+      </c>
+      <c r="G167" t="n">
+        <v>-0.02977015388089255</v>
+      </c>
+      <c r="H167" t="n">
+        <v>1.470914332175322</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0.08644662701926542</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2014-11-01</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>1.231524989320798</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.1882660152465965</v>
+      </c>
+      <c r="D168" t="n">
+        <v>1.741594755246245</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0.1116262735638029</v>
+      </c>
+      <c r="F168" t="n">
+        <v>1.085759408183207</v>
+      </c>
+      <c r="G168" t="n">
+        <v>-0.09549823379610967</v>
+      </c>
+      <c r="H168" t="n">
+        <v>1.392578536791067</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0.08845321345321011</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2014-12-01</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>0.6531213919623191</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-0.3084609444559239</v>
+      </c>
+      <c r="D169" t="n">
+        <v>1.622419504663664</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0.05261883085969643</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0.7322588005891362</v>
+      </c>
+      <c r="G169" t="n">
+        <v>-0.1757613756668053</v>
+      </c>
+      <c r="H169" t="n">
+        <v>1.356346289529387</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0.07070003431031147</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>-0.2299309782054282</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.6370316441765556</v>
+      </c>
+      <c r="D170" t="n">
+        <v>1.631625565241701</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0.09474756244156612</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0.04140186722421113</v>
+      </c>
+      <c r="G170" t="n">
+        <v>-0.4798187808896293</v>
+      </c>
+      <c r="H170" t="n">
+        <v>1.209711352352105</v>
+      </c>
+      <c r="I170" t="n">
+        <v>-0.03636401417157487</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2015-02-01</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>-0.08703146293520536</v>
+      </c>
+      <c r="C171" t="n">
+        <v>0.2534643680217386</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1.688083493871328</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0.1505352131470072</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0.1707014276846719</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0.1769197343100215</v>
+      </c>
+      <c r="H171" t="n">
+        <v>1.277481626344512</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0.114328476105352</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2015-03-01</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>-0.02203128442387348</v>
+      </c>
+      <c r="C172" t="n">
+        <v>0.2693951780812442</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1.745377707342843</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0.2427427010642358</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0.1993492743892933</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0.1890007745933397</v>
+      </c>
+      <c r="H172" t="n">
+        <v>1.280839895013131</v>
+      </c>
+      <c r="I172" t="n">
+        <v>0.1515717785806281</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2015-04-01</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>-0.1040309893939106</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0.1042478896158938</v>
+      </c>
+      <c r="D173" t="n">
+        <v>1.802827832894649</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0.2454777678552844</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.1103240640498271</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0.08865248226950229</v>
+      </c>
+      <c r="H173" t="n">
+        <v>1.294372884198181</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0.1845133202031723</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2015-05-01</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>0.03503321824429584</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0.3297745341246827</v>
+      </c>
+      <c r="D174" t="n">
+        <v>1.75094409524732</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0.141705269612924</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.1852862157349033</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0.2399736337981739</v>
+      </c>
+      <c r="H174" t="n">
+        <v>1.247201121643959</v>
+      </c>
+      <c r="I174" t="n">
+        <v>0.1220925420081231</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2015-06-01</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>0.1795718097550525</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0.2767920810460733</v>
+      </c>
+      <c r="D175" t="n">
+        <v>1.777267624465506</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0.1555724736023389</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0.2704286757220897</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0.1941907178891755</v>
+      </c>
+      <c r="H175" t="n">
+        <v>1.254154386404971</v>
+      </c>
+      <c r="I175" t="n">
+        <v>0.1198768162371078</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2015-07-01</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>0.2256861110409458</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0.1586319780187306</v>
+      </c>
+      <c r="D176" t="n">
+        <v>1.834631289489708</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0.2069700575054512</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0.2197328295222345</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0.09126707412117074</v>
+      </c>
+      <c r="H176" t="n">
+        <v>1.178950004173274</v>
+      </c>
+      <c r="I176" t="n">
+        <v>0.09908961416980056</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2015-08-01</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>0.2413037985344868</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-0.000420108051790713</v>
+      </c>
+      <c r="D177" t="n">
+        <v>1.850632327342128</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0.1038896790551025</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0.2392713007937974</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0.007171763741609105</v>
+      </c>
+      <c r="H177" t="n">
+        <v>1.221254627939716</v>
+      </c>
+      <c r="I177" t="n">
+        <v>0.08043061312874578</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2015-09-01</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>0.008842961634170088</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-0.2247587519377592</v>
+      </c>
+      <c r="D178" t="n">
+        <v>1.897096144665089</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0.2055045569296921</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0.06569964994405098</v>
+      </c>
+      <c r="G178" t="n">
+        <v>-0.1383026677047816</v>
+      </c>
+      <c r="H178" t="n">
+        <v>1.232124816431091</v>
+      </c>
+      <c r="I178" t="n">
+        <v>0.1442466205077597</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2015-10-01</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>0.1276165606705071</v>
+      </c>
+      <c r="C179" t="n">
+        <v>0.09894820166906904</v>
+      </c>
+      <c r="D179" t="n">
+        <v>1.913533535960799</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0.1857666573509276</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0.09549823379610967</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>1.177988677988662</v>
+      </c>
+      <c r="I179" t="n">
+        <v>0.03292316556235964</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2015-11-01</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>0.4363182169185187</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0.1194617491050876</v>
+      </c>
+      <c r="D180" t="n">
+        <v>1.997427523824635</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0.194036953168597</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0.2538775426298434</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0.06257886475782293</v>
+      </c>
+      <c r="H180" t="n">
+        <v>1.196702051340703</v>
+      </c>
+      <c r="I180" t="n">
+        <v>0.1069650717900217</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2015-12-01</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>0.6387247515364791</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-0.1075553426856057</v>
+      </c>
+      <c r="D181" t="n">
+        <v>2.071507279284091</v>
+      </c>
+      <c r="E181" t="n">
+        <v>0.1252860903779407</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0.345963756177925</v>
+      </c>
+      <c r="G181" t="n">
+        <v>-0.08406979843752493</v>
+      </c>
+      <c r="H181" t="n">
+        <v>1.191700692994213</v>
+      </c>
+      <c r="I181" t="n">
+        <v>0.06575432540172343</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2016-01-01</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>1.237502502694388</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-0.04584435630738959</v>
+      </c>
+      <c r="D182" t="n">
+        <v>2.145022538582464</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0.1668390943254217</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0.8711486332691809</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0.04104416351993212</v>
+      </c>
+      <c r="H182" t="n">
+        <v>1.40624025609577</v>
+      </c>
+      <c r="I182" t="n">
+        <v>0.1755718920694926</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2016-02-01</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>0.8472775790126619</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-0.1329675323582302</v>
+      </c>
+      <c r="D183" t="n">
+        <v>2.222573822094165</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0.2265722275519799</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0.640330493157748</v>
+      </c>
+      <c r="G183" t="n">
+        <v>-0.05230983835234904</v>
+      </c>
+      <c r="H183" t="n">
+        <v>1.465885968190705</v>
+      </c>
+      <c r="I183" t="n">
+        <v>0.1732143040167333</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2016-03-01</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>0.8916160965521946</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0.3134796238244419</v>
+      </c>
+      <c r="D184" t="n">
+        <v>2.142426948557663</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0.164148099873751</v>
+      </c>
+      <c r="F184" t="n">
+        <v>0.6855104733630268</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0.2339781415157338</v>
+      </c>
+      <c r="H184" t="n">
+        <v>1.457447911267762</v>
+      </c>
+      <c r="I184" t="n">
+        <v>0.143243022018491</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2016-04-01</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>1.172625750353484</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0.3830645161290169</v>
+      </c>
+      <c r="D185" t="n">
+        <v>2.156654761214183</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0.2594413471430856</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0.9259068531526138</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0.3276238059647829</v>
+      </c>
+      <c r="H185" t="n">
+        <v>1.519948679745053</v>
+      </c>
+      <c r="I185" t="n">
+        <v>0.2462299235767684</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2016-05-01</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>1.078476462124622</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0.236409586931785</v>
+      </c>
+      <c r="D186" t="n">
+        <v>2.254559597497607</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0.2376790197565759</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0.8486853596638255</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0.163276968763082</v>
+      </c>
+      <c r="H186" t="n">
+        <v>1.568732819378704</v>
+      </c>
+      <c r="I186" t="n">
+        <v>0.1702049593852228</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2016-06-01</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>1.079286534795942</v>
+      </c>
+      <c r="C187" t="n">
+        <v>0.2775957287827202</v>
+      </c>
+      <c r="D187" t="n">
+        <v>2.262211646506707</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0.1630674484192962</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0.8296074490339977</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0.1752366203783939</v>
+      </c>
+      <c r="H187" t="n">
+        <v>1.552403955327097</v>
+      </c>
+      <c r="I187" t="n">
+        <v>0.1037808798990625</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2016-07-01</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>0.8683633430518256</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-0.05037007434789409</v>
+      </c>
+      <c r="D188" t="n">
+        <v>2.170139962484297</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0.1167488082734147</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0.7550842682239489</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0.01728960081361919</v>
+      </c>
+      <c r="H188" t="n">
+        <v>1.599331807214011</v>
+      </c>
+      <c r="I188" t="n">
+        <v>0.1453458825442677</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2016-08-01</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>1.055315859565686</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0.184922178583169</v>
+      </c>
+      <c r="D189" t="n">
+        <v>2.308734561418668</v>
+      </c>
+      <c r="E189" t="n">
+        <v>0.2396813932187047</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0.8882104659263312</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0.1393097557503387</v>
+      </c>
+      <c r="H189" t="n">
+        <v>1.696958456973308</v>
+      </c>
+      <c r="I189" t="n">
+        <v>0.1765977529458507</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2016-09-01</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>1.548644620165218</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0.2623209794425208</v>
+      </c>
+      <c r="D190" t="n">
+        <v>2.271120682569183</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0.1686639320835903</v>
+      </c>
+      <c r="F190" t="n">
+        <v>1.219774921263461</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0.1898881995146207</v>
+      </c>
+      <c r="H190" t="n">
+        <v>1.685254537223768</v>
+      </c>
+      <c r="I190" t="n">
+        <v>0.1327213965127694</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2016-10-01</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>1.685924966243646</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0.2342687497926876</v>
+      </c>
+      <c r="D191" t="n">
+        <v>2.204555150799115</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0.1205584266321447</v>
+      </c>
+      <c r="F191" t="n">
+        <v>1.427003293084517</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0.2047311130480622</v>
+      </c>
+      <c r="H191" t="n">
+        <v>1.78240835973178</v>
+      </c>
+      <c r="I191" t="n">
+        <v>0.1284982900621179</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2016-11-01</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>1.684333471978894</v>
+      </c>
+      <c r="C192" t="n">
+        <v>0.1178947716771184</v>
+      </c>
+      <c r="D192" t="n">
+        <v>2.145421939805359</v>
+      </c>
+      <c r="E192" t="n">
+        <v>0.1360669818818216</v>
+      </c>
+      <c r="F192" t="n">
+        <v>1.39740408866289</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0.03337783711616638</v>
+      </c>
+      <c r="H192" t="n">
+        <v>1.718859162454289</v>
+      </c>
+      <c r="I192" t="n">
+        <v>0.04446195976193223</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2016-12-01</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>2.050798911511986</v>
+      </c>
+      <c r="C193" t="n">
+        <v>0.2524522158776188</v>
+      </c>
+      <c r="D193" t="n">
+        <v>2.197123661300271</v>
+      </c>
+      <c r="E193" t="n">
+        <v>0.1759653039710374</v>
+      </c>
+      <c r="F193" t="n">
+        <v>1.657158102117884</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0.1718890607779411</v>
+      </c>
+      <c r="H193" t="n">
+        <v>1.770093227647962</v>
+      </c>
+      <c r="I193" t="n">
+        <v>0.1161557497096233</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2017-01-01</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>2.510393348257112</v>
+      </c>
+      <c r="C194" t="n">
+        <v>0.4043076694815628</v>
+      </c>
+      <c r="D194" t="n">
+        <v>2.250209222102018</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0.2188700384122999</v>
+      </c>
+      <c r="F194" t="n">
+        <v>2.005210470173124</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0.3835633030856656</v>
+      </c>
+      <c r="H194" t="n">
+        <v>1.863334939067518</v>
+      </c>
+      <c r="I194" t="n">
+        <v>0.2673527037933887</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2017-02-01</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>2.810361681329421</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0.1592657357009752</v>
+      </c>
+      <c r="D195" t="n">
+        <v>2.235346829049734</v>
+      </c>
+      <c r="E195" t="n">
+        <v>0.2120039765717507</v>
+      </c>
+      <c r="F195" t="n">
+        <v>2.197136846426195</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0.1357452413751625</v>
+      </c>
+      <c r="H195" t="n">
+        <v>1.867275108455435</v>
+      </c>
+      <c r="I195" t="n">
+        <v>0.1770890979523987</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2017-03-01</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>2.44119623655914</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-0.04672016261895173</v>
+      </c>
+      <c r="D196" t="n">
+        <v>2.045845481938735</v>
+      </c>
+      <c r="E196" t="n">
+        <v>-0.02151411565032291</v>
+      </c>
+      <c r="F196" t="n">
+        <v>1.90636102095767</v>
+      </c>
+      <c r="G196" t="n">
+        <v>-0.05121201775349915</v>
+      </c>
+      <c r="H196" t="n">
+        <v>1.67865462421839</v>
+      </c>
+      <c r="I196" t="n">
+        <v>-0.0421851929972572</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2017-04-01</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>2.176223471915395</v>
+      </c>
+      <c r="C197" t="n">
+        <v>0.1234152821740775</v>
+      </c>
+      <c r="D197" t="n">
+        <v>1.896565010890239</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0.1127741647539038</v>
+      </c>
+      <c r="F197" t="n">
+        <v>1.76747318686028</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0.1908876274677285</v>
+      </c>
+      <c r="H197" t="n">
+        <v>1.636821345944117</v>
+      </c>
+      <c r="I197" t="n">
+        <v>0.2049859825761891</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2017-05-01</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>1.856343166761976</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.07739779600562935</v>
+      </c>
+      <c r="D198" t="n">
+        <v>1.737093191225925</v>
+      </c>
+      <c r="E198" t="n">
+        <v>0.08080341683018855</v>
+      </c>
+      <c r="F198" t="n">
+        <v>1.557772049759043</v>
+      </c>
+      <c r="G198" t="n">
+        <v>-0.04311857608422232</v>
+      </c>
+      <c r="H198" t="n">
+        <v>1.545521142810613</v>
+      </c>
+      <c r="I198" t="n">
+        <v>0.08022221553702913</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2017-06-01</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>1.640565809959127</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0.06516286618252209</v>
+      </c>
+      <c r="D199" t="n">
+        <v>1.699119334249022</v>
+      </c>
+      <c r="E199" t="n">
+        <v>0.1256811040846406</v>
+      </c>
+      <c r="F199" t="n">
+        <v>1.4655479277905</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0.08426797215144166</v>
+      </c>
+      <c r="H199" t="n">
+        <v>1.576443802980099</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0.1342645010671051</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2017-07-01</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>1.725107350656607</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0.03276499715354486</v>
+      </c>
+      <c r="D200" t="n">
+        <v>1.676962744472998</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0.09493696026947607</v>
+      </c>
+      <c r="F200" t="n">
+        <v>1.485631774826635</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0.0370867830723709</v>
+      </c>
+      <c r="H200" t="n">
+        <v>1.503110759268855</v>
+      </c>
+      <c r="I200" t="n">
+        <v>0.07304601899196239</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2017-08-01</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>1.92812155729698</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0.3848626163288182</v>
+      </c>
+      <c r="D201" t="n">
+        <v>1.655241261879947</v>
+      </c>
+      <c r="E201" t="n">
+        <v>0.2182669603349341</v>
+      </c>
+      <c r="F201" t="n">
+        <v>1.571908731810834</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0.2244421510375405</v>
+      </c>
+      <c r="H201" t="n">
+        <v>1.433593710424197</v>
+      </c>
+      <c r="I201" t="n">
+        <v>0.1079892010798833</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2017-09-01</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>2.180565230371179</v>
+      </c>
+      <c r="C202" t="n">
+        <v>0.5106389920997767</v>
+      </c>
+      <c r="D202" t="n">
+        <v>1.595389845765594</v>
+      </c>
+      <c r="E202" t="n">
+        <v>0.1096877660522466</v>
+      </c>
+      <c r="F202" t="n">
+        <v>1.757444307056133</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0.3728993171843609</v>
+      </c>
+      <c r="H202" t="n">
+        <v>1.422587368719253</v>
+      </c>
+      <c r="I202" t="n">
+        <v>0.1218562096725773</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2017-10-01</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>2.020757753132485</v>
+      </c>
+      <c r="C203" t="n">
+        <v>0.07750522450138408</v>
+      </c>
+      <c r="D203" t="n">
+        <v>1.759639081327125</v>
+      </c>
+      <c r="E203" t="n">
+        <v>0.2824233026913259</v>
+      </c>
+      <c r="F203" t="n">
+        <v>1.682040700732301</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0.1304780876494105</v>
+      </c>
+      <c r="H203" t="n">
+        <v>1.54101110538496</v>
+      </c>
+      <c r="I203" t="n">
+        <v>0.2454110135674537</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2017-11-01</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>2.172493864295566</v>
+      </c>
+      <c r="C204" t="n">
+        <v>0.2668007428251684</v>
+      </c>
+      <c r="D204" t="n">
+        <v>1.737607272698116</v>
+      </c>
+      <c r="E204" t="n">
+        <v>0.1143866901225143</v>
+      </c>
+      <c r="F204" t="n">
+        <v>1.793712904824019</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0.1432393987923941</v>
+      </c>
+      <c r="H204" t="n">
+        <v>1.545376496136552</v>
+      </c>
+      <c r="I204" t="n">
+        <v>0.04876301176282016</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2017-12-01</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>2.129930719552253</v>
+      </c>
+      <c r="C205" t="n">
+        <v>0.2106889244755106</v>
+      </c>
+      <c r="D205" t="n">
+        <v>1.770166453265043</v>
+      </c>
+      <c r="E205" t="n">
+        <v>0.2080247108141364</v>
+      </c>
+      <c r="F205" t="n">
+        <v>1.766409948420833</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0.1450211075242125</v>
+      </c>
+      <c r="H205" t="n">
+        <v>1.576876513317194</v>
+      </c>
+      <c r="I205" t="n">
+        <v>0.1472124135873276</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2018-01-01</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>2.151318868063945</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0.4253344363511546</v>
+      </c>
+      <c r="D206" t="n">
+        <v>1.891267113032846</v>
+      </c>
+      <c r="E206" t="n">
+        <v>0.3381247444406155</v>
+      </c>
+      <c r="F206" t="n">
+        <v>1.757649495731561</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0.3749218912726615</v>
+      </c>
+      <c r="H206" t="n">
+        <v>1.632037027720479</v>
+      </c>
+      <c r="I206" t="n">
+        <v>0.3218020917135966</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2018-02-01</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>2.263468931091861</v>
+      </c>
+      <c r="C207" t="n">
+        <v>0.2692287600609022</v>
+      </c>
+      <c r="D207" t="n">
+        <v>1.87770420481439</v>
+      </c>
+      <c r="E207" t="n">
+        <v>0.1986645977335888</v>
+      </c>
+      <c r="F207" t="n">
+        <v>1.837607695860854</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0.2144289963339485</v>
+      </c>
+      <c r="H207" t="n">
+        <v>1.644218117535967</v>
+      </c>
+      <c r="I207" t="n">
+        <v>0.1890958052412017</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2018-03-01</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>2.330949764649937</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0.0192362410782021</v>
+      </c>
+      <c r="D208" t="n">
+        <v>2.122784366233121</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0.2189972273386687</v>
+      </c>
+      <c r="F208" t="n">
+        <v>1.998292058070028</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0.1064920722568363</v>
+      </c>
+      <c r="H208" t="n">
+        <v>1.909183171052753</v>
+      </c>
+      <c r="I208" t="n">
+        <v>0.2183837625249652</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2018-04-01</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>2.470996302105299</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0.2604406656061986</v>
+      </c>
+      <c r="D209" t="n">
+        <v>2.150644636125887</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0.1400860807504456</v>
+      </c>
+      <c r="F209" t="n">
+        <v>2.04662822762598</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0.2383672826129724</v>
+      </c>
+      <c r="H209" t="n">
+        <v>1.88421928742617</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0.1804395626066269</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2018-05-01</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>2.781921607842497</v>
+      </c>
+      <c r="C210" t="n">
+        <v>0.2257949781598212</v>
+      </c>
+      <c r="D210" t="n">
+        <v>2.272998448872432</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0.2006780189377722</v>
+      </c>
+      <c r="F210" t="n">
+        <v>2.266206536786974</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0.1719631311046799</v>
+      </c>
+      <c r="H210" t="n">
+        <v>1.980902377684046</v>
+      </c>
+      <c r="I210" t="n">
+        <v>0.1751934017046874</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2018-06-01</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>2.807550693594019</v>
+      </c>
+      <c r="C211" t="n">
+        <v>0.09011451720948305</v>
+      </c>
+      <c r="D211" t="n">
+        <v>2.245517307127032</v>
+      </c>
+      <c r="E211" t="n">
+        <v>0.0987769546364925</v>
+      </c>
+      <c r="F211" t="n">
+        <v>2.268307840346395</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0.08632444256970739</v>
+      </c>
+      <c r="H211" t="n">
+        <v>1.936219818485641</v>
+      </c>
+      <c r="I211" t="n">
+        <v>0.09039103949695093</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2018-07-01</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>2.854124785561929</v>
+      </c>
+      <c r="C212" t="n">
+        <v>0.07808204989283585</v>
+      </c>
+      <c r="D212" t="n">
+        <v>2.267595293370639</v>
+      </c>
+      <c r="E212" t="n">
+        <v>0.1165505693495383</v>
+      </c>
+      <c r="F212" t="n">
+        <v>2.338607055900122</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0.1058522576914411</v>
+      </c>
+      <c r="H212" t="n">
+        <v>1.995800419957994</v>
+      </c>
+      <c r="I212" t="n">
+        <v>0.1315376158316228</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2018-08-01</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>2.642923856874257</v>
+      </c>
+      <c r="C213" t="n">
+        <v>0.1787320770339385</v>
+      </c>
+      <c r="D213" t="n">
+        <v>2.120894133486462</v>
+      </c>
+      <c r="E213" t="n">
+        <v>0.07450552776688824</v>
+      </c>
+      <c r="F213" t="n">
+        <v>2.180411288951989</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0.06951447565524127</v>
+      </c>
+      <c r="H213" t="n">
+        <v>1.895762999660411</v>
+      </c>
+      <c r="I213" t="n">
+        <v>0.009803344901282429</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2018-09-01</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>2.332055105808828</v>
+      </c>
+      <c r="C214" t="n">
+        <v>0.2062281702117419</v>
+      </c>
+      <c r="D214" t="n">
+        <v>2.197680489850162</v>
+      </c>
+      <c r="E214" t="n">
+        <v>0.184961863733113</v>
+      </c>
+      <c r="F214" t="n">
+        <v>2.009960159362545</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0.2054633688165497</v>
+      </c>
+      <c r="H214" t="n">
+        <v>1.960295291300884</v>
+      </c>
+      <c r="I214" t="n">
+        <v>0.1852650564617253</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2018-10-01</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>2.492032470218053</v>
+      </c>
+      <c r="C215" t="n">
+        <v>0.2339580144498754</v>
+      </c>
+      <c r="D215" t="n">
+        <v>2.126409125691242</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0.212487614565271</v>
+      </c>
+      <c r="F215" t="n">
+        <v>2.053098049357893</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0.1728211837762839</v>
+      </c>
+      <c r="H215" t="n">
+        <v>1.870907390084176</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0.157526539797459</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2018-11-01</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>2.147328577667773</v>
+      </c>
+      <c r="C216" t="n">
+        <v>-0.07041919199911595</v>
+      </c>
+      <c r="D216" t="n">
+        <v>2.215384372931584</v>
+      </c>
+      <c r="E216" t="n">
+        <v>0.2016090098371448</v>
+      </c>
+      <c r="F216" t="n">
+        <v>1.941892227464614</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0.0341147229397043</v>
+      </c>
+      <c r="H216" t="n">
+        <v>2.01024518824291</v>
+      </c>
+      <c r="I216" t="n">
+        <v>0.1856085028232091</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2018-12-01</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>2.002380904340106</v>
+      </c>
+      <c r="C217" t="n">
+        <v>0.06848935445813442</v>
+      </c>
+      <c r="D217" t="n">
+        <v>2.248529550529987</v>
+      </c>
+      <c r="E217" t="n">
+        <v>0.2405189659226092</v>
+      </c>
+      <c r="F217" t="n">
+        <v>1.864690887811071</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0.06918055149565117</v>
+      </c>
+      <c r="H217" t="n">
+        <v>2.038079914186097</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0.1745387885643046</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>1.487589357829133</v>
+      </c>
+      <c r="C218" t="n">
+        <v>-0.08149798035343991</v>
+      </c>
+      <c r="D218" t="n">
+        <v>2.179432924248847</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0.270319114983697</v>
+      </c>
+      <c r="F218" t="n">
+        <v>1.431832330358995</v>
+      </c>
+      <c r="G218" t="n">
+        <v>-0.05160611873301635</v>
+      </c>
+      <c r="H218" t="n">
+        <v>1.844426623897344</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0.1314060446780507</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2019-02-01</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>1.518861535132188</v>
+      </c>
+      <c r="C219" t="n">
+        <v>0.3001255142321968</v>
+      </c>
+      <c r="D219" t="n">
+        <v>2.141088963712923</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0.161063942385109</v>
+      </c>
+      <c r="F219" t="n">
+        <v>1.400173542636263</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0.1831501831501825</v>
+      </c>
+      <c r="H219" t="n">
+        <v>1.744105614735481</v>
+      </c>
+      <c r="I219" t="n">
+        <v>0.09040536599591587</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2019-03-01</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>1.883186351306398</v>
+      </c>
+      <c r="C220" t="n">
+        <v>0.3781792917230797</v>
+      </c>
+      <c r="D220" t="n">
+        <v>2.06656235001228</v>
+      </c>
+      <c r="E220" t="n">
+        <v>0.1458730559831034</v>
+      </c>
+      <c r="F220" t="n">
+        <v>1.521807651392781</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0.2265743513944596</v>
+      </c>
+      <c r="H220" t="n">
+        <v>1.61606799514884</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0.09226615386110915</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>2.000583470209061</v>
+      </c>
+      <c r="C221" t="n">
+        <v>0.3759679404743643</v>
+      </c>
+      <c r="D221" t="n">
+        <v>2.091337723570907</v>
+      </c>
+      <c r="E221" t="n">
+        <v>0.1643938264383582</v>
+      </c>
+      <c r="F221" t="n">
+        <v>1.566338462747874</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0.2823351347155834</v>
+      </c>
+      <c r="H221" t="n">
+        <v>1.636778803566852</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0.2008577694113889</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2019-05-01</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>1.795910555360614</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0.02468332856644384</v>
+      </c>
+      <c r="D222" t="n">
+        <v>1.97242800754438</v>
+      </c>
+      <c r="E222" t="n">
+        <v>0.08397042714227698</v>
+      </c>
+      <c r="F222" t="n">
+        <v>1.465553604535952</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0.07256191950464341</v>
+      </c>
+      <c r="H222" t="n">
+        <v>1.563175476517964</v>
+      </c>
+      <c r="I222" t="n">
+        <v>0.1026485256379273</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>1.671194894390049</v>
+      </c>
+      <c r="C223" t="n">
+        <v>-0.03251128102280676</v>
+      </c>
+      <c r="D223" t="n">
+        <v>2.074600134421645</v>
+      </c>
+      <c r="E223" t="n">
+        <v>0.1990717611749071</v>
+      </c>
+      <c r="F223" t="n">
+        <v>1.426065138343025</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0.04737274616908316</v>
+      </c>
+      <c r="H223" t="n">
+        <v>1.656981309879058</v>
+      </c>
+      <c r="I223" t="n">
+        <v>0.1828365789244613</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2019-07-01</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>1.826331335037068</v>
+      </c>
+      <c r="C224" t="n">
+        <v>0.2307876166182776</v>
+      </c>
+      <c r="D224" t="n">
+        <v>2.165704950349046</v>
+      </c>
+      <c r="E224" t="n">
+        <v>0.2059077639787077</v>
+      </c>
+      <c r="F224" t="n">
+        <v>1.453929526028763</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0.1333539484364765</v>
+      </c>
+      <c r="H224" t="n">
+        <v>1.639119267494071</v>
+      </c>
+      <c r="I224" t="n">
+        <v>0.113943607570488</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2019-08-01</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>1.737641210666641</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0.09147700174354512</v>
+      </c>
+      <c r="D225" t="n">
+        <v>2.321135673598529</v>
+      </c>
+      <c r="E225" t="n">
+        <v>0.2267547857794039</v>
+      </c>
+      <c r="F225" t="n">
+        <v>1.430416405760804</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0.04632220956939381</v>
+      </c>
+      <c r="H225" t="n">
+        <v>1.745804579673771</v>
+      </c>
+      <c r="I225" t="n">
+        <v>0.1147784486583481</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2019-09-01</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>1.684497704039156</v>
+      </c>
+      <c r="C226" t="n">
+        <v>0.1538846099767177</v>
+      </c>
+      <c r="D226" t="n">
+        <v>2.330009908347774</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0.1936508297426309</v>
+      </c>
+      <c r="F226" t="n">
+        <v>1.283953992462261</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0.06076975016879871</v>
+      </c>
+      <c r="H226" t="n">
+        <v>1.632014089330269</v>
+      </c>
+      <c r="I226" t="n">
+        <v>0.07321984257735448</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2019-10-01</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>1.733973699618629</v>
+      </c>
+      <c r="C227" t="n">
+        <v>0.2827282299262768</v>
+      </c>
+      <c r="D227" t="n">
+        <v>2.337814820965822</v>
+      </c>
+      <c r="E227" t="n">
+        <v>0.2201310195621753</v>
+      </c>
+      <c r="F227" t="n">
+        <v>1.288561820751499</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0.1773784620130447</v>
+      </c>
+      <c r="H227" t="n">
+        <v>1.623585956274542</v>
+      </c>
+      <c r="I227" t="n">
+        <v>0.1492206829493803</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2019-11-01</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>2.092290394862917</v>
+      </c>
+      <c r="C228" t="n">
+        <v>0.281542260504386</v>
+      </c>
+      <c r="D228" t="n">
+        <v>2.35469609426493</v>
+      </c>
+      <c r="E228" t="n">
+        <v>0.2181379024040364</v>
+      </c>
+      <c r="F228" t="n">
+        <v>1.358277306830358</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0.1029667908041931</v>
+      </c>
+      <c r="H228" t="n">
+        <v>1.497718319747254</v>
+      </c>
+      <c r="I228" t="n">
+        <v>0.06152189795054497</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2019-12-01</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>2.319527469962446</v>
+      </c>
+      <c r="C229" t="n">
+        <v>0.2912218521089249</v>
+      </c>
+      <c r="D229" t="n">
+        <v>2.290598816440625</v>
+      </c>
+      <c r="E229" t="n">
+        <v>0.1777456429722601</v>
+      </c>
+      <c r="F229" t="n">
+        <v>1.563762767645893</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0.2720526032454096</v>
+      </c>
+      <c r="H229" t="n">
+        <v>1.544751058548699</v>
+      </c>
+      <c r="I229" t="n">
+        <v>0.2209583829689166</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>2.599767976845202</v>
+      </c>
+      <c r="C230" t="n">
+        <v>0.1921664153423874</v>
+      </c>
+      <c r="D230" t="n">
+        <v>2.281739183789289</v>
+      </c>
+      <c r="E230" t="n">
+        <v>0.2616344635741674</v>
+      </c>
+      <c r="F230" t="n">
+        <v>1.794482113631046</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0.1754436423250461</v>
+      </c>
+      <c r="H230" t="n">
+        <v>1.59132886167006</v>
+      </c>
+      <c r="I230" t="n">
+        <v>0.1773355572170843</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2020-02-01</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>2.34131667975952</v>
+      </c>
+      <c r="C231" t="n">
+        <v>0.04746707213065804</v>
+      </c>
+      <c r="D231" t="n">
+        <v>2.367661360103535</v>
+      </c>
+      <c r="E231" t="n">
+        <v>0.2452046371421268</v>
+      </c>
+      <c r="F231" t="n">
+        <v>1.689097203314005</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0.07943343860656871</v>
+      </c>
+      <c r="H231" t="n">
+        <v>1.69769723104416</v>
+      </c>
+      <c r="I231" t="n">
+        <v>0.1952022352569527</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2020-03-01</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>1.494039964290916</v>
+      </c>
+      <c r="C232" t="n">
+        <v>-0.4528447444551498</v>
+      </c>
+      <c r="D232" t="n">
+        <v>2.097741687598198</v>
+      </c>
+      <c r="E232" t="n">
+        <v>-0.1181882784156874</v>
+      </c>
+      <c r="F232" t="n">
+        <v>1.166209044426547</v>
+      </c>
+      <c r="G232" t="n">
+        <v>-0.2887934744149945</v>
+      </c>
+      <c r="H232" t="n">
+        <v>1.527295309437404</v>
+      </c>
+      <c r="I232" t="n">
+        <v>-0.0754457506852102</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>0.3130472940411133</v>
+      </c>
+      <c r="C233" t="n">
+        <v>-0.7920147553434065</v>
+      </c>
+      <c r="D233" t="n">
+        <v>1.430932415256647</v>
+      </c>
+      <c r="E233" t="n">
+        <v>-0.489788582084516</v>
+      </c>
+      <c r="F233" t="n">
+        <v>0.4624613003096023</v>
+      </c>
+      <c r="G233" t="n">
+        <v>-0.415264071505983</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0.9954970222243897</v>
+      </c>
+      <c r="I233" t="n">
+        <v>-0.3239926599892917</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2020-05-01</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>0.1982013035848551</v>
+      </c>
+      <c r="C234" t="n">
+        <v>-0.08983252093487382</v>
+      </c>
+      <c r="D234" t="n">
+        <v>1.218456469260198</v>
+      </c>
+      <c r="E234" t="n">
+        <v>-0.1256839237467333</v>
+      </c>
+      <c r="F234" t="n">
+        <v>0.4901629042393774</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0.1001560122498413</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0.9973783749794407</v>
+      </c>
+      <c r="I234" t="n">
+        <v>0.1045132463348475</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>0.7166562831830481</v>
+      </c>
+      <c r="C235" t="n">
+        <v>0.4847499237691677</v>
+      </c>
+      <c r="D235" t="n">
+        <v>1.183684188491241</v>
+      </c>
+      <c r="E235" t="n">
+        <v>0.1646496767290229</v>
+      </c>
+      <c r="F235" t="n">
+        <v>0.7595377063120967</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0.3155606011044698</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0.9704519119350996</v>
+      </c>
+      <c r="I235" t="n">
+        <v>0.1561272772552247</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>0.9968647625897997</v>
+      </c>
+      <c r="C236" t="n">
+        <v>0.5096443382793581</v>
+      </c>
+      <c r="D236" t="n">
+        <v>1.560695837131587</v>
+      </c>
+      <c r="E236" t="n">
+        <v>0.5792762056656242</v>
+      </c>
+      <c r="F236" t="n">
+        <v>0.9225840072571545</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0.2953869761197048</v>
+      </c>
+      <c r="H236" t="n">
+        <v>1.214336696309726</v>
+      </c>
+      <c r="I236" t="n">
+        <v>0.3557595753837406</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2020-08-01</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>1.281069849552385</v>
+      </c>
+      <c r="C237" t="n">
+        <v>0.3731343283582156</v>
+      </c>
+      <c r="D237" t="n">
+        <v>1.722393387828425</v>
+      </c>
+      <c r="E237" t="n">
+        <v>0.3863285325873544</v>
+      </c>
+      <c r="F237" t="n">
+        <v>1.157519050834388</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0.2792174262273184</v>
+      </c>
+      <c r="H237" t="n">
+        <v>1.393103846931987</v>
+      </c>
+      <c r="I237" t="n">
+        <v>0.29160353354869</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>1.391022891237381</v>
+      </c>
+      <c r="C238" t="n">
+        <v>0.2626139536318739</v>
+      </c>
+      <c r="D238" t="n">
+        <v>1.719064405343662</v>
+      </c>
+      <c r="E238" t="n">
+        <v>0.1903718771188556</v>
+      </c>
+      <c r="F238" t="n">
+        <v>1.27635371578958</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0.1783160102984516</v>
+      </c>
+      <c r="H238" t="n">
+        <v>1.479691546407635</v>
+      </c>
+      <c r="I238" t="n">
+        <v>0.1586803872941633</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>1.230386342867162</v>
+      </c>
+      <c r="C239" t="n">
+        <v>0.1238475828567287</v>
+      </c>
+      <c r="D239" t="n">
+        <v>1.636411669245552</v>
+      </c>
+      <c r="E239" t="n">
+        <v>0.1386962552011095</v>
+      </c>
+      <c r="F239" t="n">
+        <v>1.187486166844698</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0.08947523725215678</v>
+      </c>
+      <c r="H239" t="n">
+        <v>1.421732610451021</v>
+      </c>
+      <c r="I239" t="n">
+        <v>0.09202162982639983</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2020-11-01</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>1.175745213840584</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0.2274132890799363</v>
+      </c>
+      <c r="D240" t="n">
+        <v>1.669378040881497</v>
+      </c>
+      <c r="E240" t="n">
+        <v>0.2506442485499916</v>
+      </c>
+      <c r="F240" t="n">
+        <v>1.186264708144269</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0.1017584236003399</v>
+      </c>
+      <c r="H240" t="n">
+        <v>1.453521884486797</v>
+      </c>
+      <c r="I240" t="n">
+        <v>0.09288483228599986</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2020-12-01</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>1.320419131577943</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0.4346309661148906</v>
+      </c>
+      <c r="D241" t="n">
+        <v>1.624313961356294</v>
+      </c>
+      <c r="E241" t="n">
+        <v>0.1333427167097057</v>
+      </c>
+      <c r="F241" t="n">
+        <v>1.334522131784066</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0.4189705295559509</v>
+      </c>
+      <c r="H241" t="n">
+        <v>1.508790092214496</v>
+      </c>
+      <c r="I241" t="n">
+        <v>0.2755551347000562</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>1.37384371370024</v>
+      </c>
+      <c r="C242" t="n">
+        <v>0.2449960884580937</v>
+      </c>
+      <c r="D242" t="n">
+        <v>1.376370371481284</v>
+      </c>
+      <c r="E242" t="n">
+        <v>0.01701554703132935</v>
+      </c>
+      <c r="F242" t="n">
+        <v>1.585797683988899</v>
+      </c>
+      <c r="G242" t="n">
+        <v>0.4238450694897811</v>
+      </c>
+      <c r="H242" t="n">
+        <v>1.697493947773832</v>
+      </c>
+      <c r="I242" t="n">
+        <v>0.3635642517186621</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2021-02-01</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>1.669816779170685</v>
+      </c>
+      <c r="C243" t="n">
+        <v>0.3395676223033384</v>
+      </c>
+      <c r="D243" t="n">
+        <v>1.280248344990098</v>
+      </c>
+      <c r="E243" t="n">
+        <v>0.150155147991593</v>
+      </c>
+      <c r="F243" t="n">
+        <v>1.842731871515602</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0.332557679444534</v>
+      </c>
+      <c r="H243" t="n">
+        <v>1.709467009196741</v>
+      </c>
+      <c r="I243" t="n">
+        <v>0.2069984286937387</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2021-03-01</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>2.667818782064191</v>
+      </c>
+      <c r="C244" t="n">
+        <v>0.5243209815652961</v>
+      </c>
+      <c r="D244" t="n">
+        <v>1.649479131561415</v>
+      </c>
+      <c r="E244" t="n">
+        <v>0.2459443190924393</v>
+      </c>
+      <c r="F244" t="n">
+        <v>2.669006722866385</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0.5201877934272403</v>
+      </c>
+      <c r="H244" t="n">
+        <v>2.199136019573356</v>
+      </c>
+      <c r="I244" t="n">
+        <v>0.4056299940845554</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>4.133077115360573</v>
+      </c>
+      <c r="C245" t="n">
+        <v>0.6238653990587206</v>
+      </c>
+      <c r="D245" t="n">
+        <v>2.97803165428645</v>
+      </c>
+      <c r="E245" t="n">
+        <v>0.8108038414641028</v>
+      </c>
+      <c r="F245" t="n">
+        <v>3.640285829850343</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0.526836923421814</v>
+      </c>
+      <c r="H245" t="n">
+        <v>3.130603204433657</v>
+      </c>
+      <c r="I245" t="n">
+        <v>0.5844781311662439</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2021-05-01</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>4.918257089467626</v>
+      </c>
+      <c r="C246" t="n">
+        <v>0.6635060424433847</v>
+      </c>
+      <c r="D246" t="n">
+        <v>3.787696110198491</v>
+      </c>
+      <c r="E246" t="n">
+        <v>0.6595775780164903</v>
+      </c>
+      <c r="F246" t="n">
+        <v>4.07246348925363</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0.5175714099871831</v>
+      </c>
+      <c r="H246" t="n">
+        <v>3.541119901917589</v>
+      </c>
+      <c r="I246" t="n">
+        <v>0.5029844363041214</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>5.295632620349999</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0.8461787818155431</v>
+      </c>
+      <c r="D247" t="n">
+        <v>4.439362194328367</v>
+      </c>
+      <c r="E247" t="n">
+        <v>0.7935672408473149</v>
+      </c>
+      <c r="F247" t="n">
+        <v>4.306128320705871</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0.5407903859486973</v>
+      </c>
+      <c r="H247" t="n">
+        <v>3.861712810213747</v>
+      </c>
+      <c r="I247" t="n">
+        <v>0.4662392806593862</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>5.245169381309234</v>
+      </c>
+      <c r="C248" t="n">
+        <v>0.4614747980816958</v>
+      </c>
+      <c r="D248" t="n">
+        <v>4.210719214328185</v>
+      </c>
+      <c r="E248" t="n">
+        <v>0.359083885885525</v>
+      </c>
+      <c r="F248" t="n">
+        <v>4.473216164011551</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0.4560500183891092</v>
+      </c>
+      <c r="H248" t="n">
+        <v>3.92711817566731</v>
+      </c>
+      <c r="I248" t="n">
+        <v>0.418957119048291</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>5.152015301793966</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0.2842925602144719</v>
+      </c>
+      <c r="D249" t="n">
+        <v>3.939691977557724</v>
+      </c>
+      <c r="E249" t="n">
+        <v>0.1252476242427747</v>
+      </c>
+      <c r="F249" t="n">
+        <v>4.580909697720981</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0.3825876839715914</v>
+      </c>
+      <c r="H249" t="n">
+        <v>3.958458044715574</v>
+      </c>
+      <c r="I249" t="n">
+        <v>0.3218470905389736</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>5.351215590949132</v>
+      </c>
+      <c r="C250" t="n">
+        <v>0.4525517463950024</v>
+      </c>
+      <c r="D250" t="n">
+        <v>4.002855729865806</v>
+      </c>
+      <c r="E250" t="n">
+        <v>0.2512571819768494</v>
+      </c>
+      <c r="F250" t="n">
+        <v>4.737428253233955</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0.3282455276546914</v>
+      </c>
+      <c r="H250" t="n">
+        <v>4.013850678303776</v>
+      </c>
+      <c r="I250" t="n">
+        <v>0.2120483689641572</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>6.235042390298062</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0.9638202329232071</v>
+      </c>
+      <c r="D251" t="n">
+        <v>4.590317334184912</v>
+      </c>
+      <c r="E251" t="n">
+        <v>0.704331099972122</v>
+      </c>
+      <c r="F251" t="n">
+        <v>5.336135652537788</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0.6616136830434272</v>
+      </c>
+      <c r="H251" t="n">
+        <v>4.436672448273571</v>
+      </c>
+      <c r="I251" t="n">
+        <v>0.498900958583004</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>6.901970403700863</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0.8566262881938069</v>
+      </c>
+      <c r="D252" t="n">
+        <v>4.972572143965692</v>
+      </c>
+      <c r="E252" t="n">
+        <v>0.6170384992260303</v>
+      </c>
+      <c r="F252" t="n">
+        <v>5.93019057933839</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0.666293494158654</v>
+      </c>
+      <c r="H252" t="n">
+        <v>4.8908669097107</v>
+      </c>
+      <c r="I252" t="n">
+        <v>0.5281881874614314</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2021-12-01</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>7.174340285065539</v>
+      </c>
+      <c r="C253" t="n">
+        <v>0.6905230550805275</v>
+      </c>
+      <c r="D253" t="n">
+        <v>5.488993530393094</v>
+      </c>
+      <c r="E253" t="n">
+        <v>0.6259571074712644</v>
+      </c>
+      <c r="F253" t="n">
+        <v>6.141969176624196</v>
+      </c>
+      <c r="G253" t="n">
+        <v>0.6197309417040442</v>
+      </c>
+      <c r="H253" t="n">
+        <v>5.214550124650597</v>
+      </c>
+      <c r="I253" t="n">
+        <v>0.5849959375282099</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>7.558805726967832</v>
+      </c>
+      <c r="C254" t="n">
+        <v>0.6046039630400957</v>
+      </c>
+      <c r="D254" t="n">
+        <v>6.05428515424189</v>
+      </c>
+      <c r="E254" t="n">
+        <v>0.5529840802300345</v>
+      </c>
+      <c r="F254" t="n">
+        <v>6.272433512016362</v>
+      </c>
+      <c r="G254" t="n">
+        <v>0.547280976192388</v>
+      </c>
+      <c r="H254" t="n">
+        <v>5.35843659732218</v>
+      </c>
+      <c r="I254" t="n">
+        <v>0.5008167441526545</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2022-02-01</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>7.937278766517819</v>
+      </c>
+      <c r="C255" t="n">
+        <v>0.6926379347568234</v>
+      </c>
+      <c r="D255" t="n">
+        <v>6.455115161765645</v>
+      </c>
+      <c r="E255" t="n">
+        <v>0.5286706165847699</v>
+      </c>
+      <c r="F255" t="n">
+        <v>6.545539906103293</v>
+      </c>
+      <c r="G255" t="n">
+        <v>0.5903993617304204</v>
+      </c>
+      <c r="H255" t="n">
+        <v>5.602764293293028</v>
+      </c>
+      <c r="I255" t="n">
+        <v>0.4393798671143756</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>8.572204966013853</v>
+      </c>
+      <c r="C256" t="n">
+        <v>1.115641476274165</v>
+      </c>
+      <c r="D256" t="n">
+        <v>6.482378554404167</v>
+      </c>
+      <c r="E256" t="n">
+        <v>0.2716175292170719</v>
+      </c>
+      <c r="F256" t="n">
+        <v>6.926410970164576</v>
+      </c>
+      <c r="G256" t="n">
+        <v>0.8795198773254853</v>
+      </c>
+      <c r="H256" t="n">
+        <v>5.593221924008485</v>
+      </c>
+      <c r="I256" t="n">
+        <v>0.3965572429491138</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>8.231750770777225</v>
+      </c>
+      <c r="C257" t="n">
+        <v>0.3083351293478032</v>
+      </c>
+      <c r="D257" t="n">
+        <v>6.158737119052837</v>
+      </c>
+      <c r="E257" t="n">
+        <v>0.5044005313849409</v>
+      </c>
+      <c r="F257" t="n">
+        <v>6.684755338326309</v>
+      </c>
+      <c r="G257" t="n">
+        <v>0.2996444452209701</v>
+      </c>
+      <c r="H257" t="n">
+        <v>5.345023150300299</v>
+      </c>
+      <c r="I257" t="n">
+        <v>0.348052500132856</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>8.538171195642065</v>
+      </c>
+      <c r="C258" t="n">
+        <v>0.9484996239963239</v>
+      </c>
+      <c r="D258" t="n">
+        <v>6.025447879040891</v>
+      </c>
+      <c r="E258" t="n">
+        <v>0.5331928925972562</v>
+      </c>
+      <c r="F258" t="n">
+        <v>6.794545874740021</v>
+      </c>
+      <c r="G258" t="n">
+        <v>0.6210152248893985</v>
+      </c>
+      <c r="H258" t="n">
+        <v>5.184136763522318</v>
+      </c>
+      <c r="I258" t="n">
+        <v>0.3494929704254801</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2022-06-01</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>8.979361103105798</v>
+      </c>
+      <c r="C259" t="n">
+        <v>1.256101998640569</v>
+      </c>
+      <c r="D259" t="n">
+        <v>5.906335651591377</v>
+      </c>
+      <c r="E259" t="n">
+        <v>0.6803326679517774</v>
+      </c>
+      <c r="F259" t="n">
+        <v>7.243471864656126</v>
+      </c>
+      <c r="G259" t="n">
+        <v>0.9634278294741394</v>
+      </c>
+      <c r="H259" t="n">
+        <v>5.31569109508947</v>
+      </c>
+      <c r="I259" t="n">
+        <v>0.59189291399524</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>8.462576727730099</v>
+      </c>
+      <c r="C260" t="n">
+        <v>-0.01491742864213608</v>
+      </c>
+      <c r="D260" t="n">
+        <v>5.899916740834321</v>
+      </c>
+      <c r="E260" t="n">
+        <v>0.3530011902737717</v>
+      </c>
+      <c r="F260" t="n">
+        <v>6.750201361938934</v>
+      </c>
+      <c r="G260" t="n">
+        <v>-0.006001474648065219</v>
+      </c>
+      <c r="H260" t="n">
+        <v>5.107374057840786</v>
+      </c>
+      <c r="I260" t="n">
+        <v>0.220325942505406</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>8.222579178218826</v>
+      </c>
+      <c r="C261" t="n">
+        <v>0.06239128149656548</v>
+      </c>
+      <c r="D261" t="n">
+        <v>6.286089097732228</v>
+      </c>
+      <c r="E261" t="n">
+        <v>0.4903621970395289</v>
+      </c>
+      <c r="F261" t="n">
+        <v>6.63967758994839</v>
+      </c>
+      <c r="G261" t="n">
+        <v>0.2786566178803351</v>
+      </c>
+      <c r="H261" t="n">
+        <v>5.362447330658338</v>
+      </c>
+      <c r="I261" t="n">
+        <v>0.5653069058170646</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>8.192106896425821</v>
+      </c>
+      <c r="C262" t="n">
+        <v>0.4242672748282716</v>
+      </c>
+      <c r="D262" t="n">
+        <v>6.624287624509306</v>
+      </c>
+      <c r="E262" t="n">
+        <v>0.5702530898544778</v>
+      </c>
+      <c r="F262" t="n">
+        <v>6.667939000672507</v>
+      </c>
+      <c r="G262" t="n">
+        <v>0.3548342966585682</v>
+      </c>
+      <c r="H262" t="n">
+        <v>5.606479327988612</v>
+      </c>
+      <c r="I262" t="n">
+        <v>0.4441514278774372</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>7.758813957693</v>
+      </c>
+      <c r="C263" t="n">
+        <v>0.5594754832984217</v>
+      </c>
+      <c r="D263" t="n">
+        <v>6.294999786983246</v>
+      </c>
+      <c r="E263" t="n">
+        <v>0.3933258669599482</v>
+      </c>
+      <c r="F263" t="n">
+        <v>6.461602354598139</v>
+      </c>
+      <c r="G263" t="n">
+        <v>0.4668955704560718</v>
+      </c>
+      <c r="H263" t="n">
+        <v>5.459759683450094</v>
+      </c>
+      <c r="I263" t="n">
+        <v>0.3592772998929128</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>7.122856456533988</v>
+      </c>
+      <c r="C264" t="n">
+        <v>0.2614032556282231</v>
+      </c>
+      <c r="D264" t="n">
+        <v>5.969880665899807</v>
+      </c>
+      <c r="E264" t="n">
+        <v>0.3092862701612242</v>
+      </c>
+      <c r="F264" t="n">
+        <v>6.030493273542614</v>
+      </c>
+      <c r="G264" t="n">
+        <v>0.258652125611647</v>
+      </c>
+      <c r="H264" t="n">
+        <v>5.20808883271644</v>
+      </c>
+      <c r="I264" t="n">
+        <v>0.2882861175174778</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>6.404600402357152</v>
+      </c>
+      <c r="C265" t="n">
+        <v>0.01539563433359259</v>
+      </c>
+      <c r="D265" t="n">
+        <v>5.685531944736666</v>
+      </c>
+      <c r="E265" t="n">
+        <v>0.3559477232997654</v>
+      </c>
+      <c r="F265" t="n">
+        <v>5.520050627946982</v>
+      </c>
+      <c r="G265" t="n">
+        <v>0.1353363107321703</v>
+      </c>
+      <c r="H265" t="n">
+        <v>4.966881473370544</v>
+      </c>
+      <c r="I265" t="n">
+        <v>0.3543878015085156</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>6.327178517960097</v>
+      </c>
+      <c r="C266" t="n">
+        <v>0.5314022594635093</v>
+      </c>
+      <c r="D266" t="n">
+        <v>5.539533472591773</v>
+      </c>
+      <c r="E266" t="n">
+        <v>0.4140759271916483</v>
+      </c>
+      <c r="F266" t="n">
+        <v>5.507734586232882</v>
+      </c>
+      <c r="G266" t="n">
+        <v>0.5355453439654045</v>
+      </c>
+      <c r="H266" t="n">
+        <v>4.937665213974429</v>
+      </c>
+      <c r="I266" t="n">
+        <v>0.4728435597510128</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>5.957820738137087</v>
+      </c>
+      <c r="C267" t="n">
+        <v>0.3428533386591992</v>
+      </c>
+      <c r="D267" t="n">
+        <v>5.498260329618088</v>
+      </c>
+      <c r="E267" t="n">
+        <v>0.4893570621394172</v>
+      </c>
+      <c r="F267" t="n">
+        <v>5.197803844154003</v>
+      </c>
+      <c r="G267" t="n">
+        <v>0.2949133744475585</v>
+      </c>
+      <c r="H267" t="n">
+        <v>4.855603371625716</v>
+      </c>
+      <c r="I267" t="n">
+        <v>0.3608357091187564</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>4.917719362889961</v>
+      </c>
+      <c r="C268" t="n">
+        <v>0.1230718195389002</v>
+      </c>
+      <c r="D268" t="n">
+        <v>5.566741392671326</v>
+      </c>
+      <c r="E268" t="n">
+        <v>0.3367058722950844</v>
+      </c>
+      <c r="F268" t="n">
+        <v>4.428273156924578</v>
+      </c>
+      <c r="G268" t="n">
+        <v>0.14157779658035</v>
+      </c>
+      <c r="H268" t="n">
+        <v>4.783286394955444</v>
+      </c>
+      <c r="I268" t="n">
+        <v>0.3273155881929002</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>4.950079879124369</v>
+      </c>
+      <c r="C269" t="n">
+        <v>0.3392739405144063</v>
+      </c>
+      <c r="D269" t="n">
+        <v>5.514364195873522</v>
+      </c>
+      <c r="E269" t="n">
+        <v>0.4545350273802429</v>
+      </c>
+      <c r="F269" t="n">
+        <v>4.476012960317743</v>
+      </c>
+      <c r="G269" t="n">
+        <v>0.3454968294600791</v>
+      </c>
+      <c r="H269" t="n">
+        <v>4.789642299240104</v>
+      </c>
+      <c r="I269" t="n">
+        <v>0.3541393737057863</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>4.131851231385042</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0.1614687381333635</v>
+      </c>
+      <c r="D270" t="n">
+        <v>5.337547036084689</v>
+      </c>
+      <c r="E270" t="n">
+        <v>0.3647229997324919</v>
+      </c>
+      <c r="F270" t="n">
+        <v>4.003462454014284</v>
+      </c>
+      <c r="G270" t="n">
+        <v>0.1659010762728119</v>
+      </c>
+      <c r="H270" t="n">
+        <v>4.731625374880166</v>
+      </c>
+      <c r="I270" t="n">
+        <v>0.2939343406269446</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>3.070617072997095</v>
+      </c>
+      <c r="C271" t="n">
+        <v>0.224175331482801</v>
+      </c>
+      <c r="D271" t="n">
+        <v>4.853596327155252</v>
+      </c>
+      <c r="E271" t="n">
+        <v>0.2177785289873002</v>
+      </c>
+      <c r="F271" t="n">
+        <v>3.284521339529123</v>
+      </c>
+      <c r="G271" t="n">
+        <v>0.2655014565126734</v>
+      </c>
+      <c r="H271" t="n">
+        <v>4.383786808421353</v>
+      </c>
+      <c r="I271" t="n">
+        <v>0.2578033808352087</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>3.287749268428297</v>
+      </c>
+      <c r="C272" t="n">
+        <v>0.1957146710348745</v>
+      </c>
+      <c r="D272" t="n">
+        <v>4.700970557935236</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0.2069265248668462</v>
+      </c>
+      <c r="F272" t="n">
+        <v>3.40904219289897</v>
+      </c>
+      <c r="G272" t="n">
+        <v>0.1145522914608677</v>
+      </c>
+      <c r="H272" t="n">
+        <v>4.299124123250864</v>
+      </c>
+      <c r="I272" t="n">
+        <v>0.1390401206131209</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>3.722504803505289</v>
+      </c>
+      <c r="C273" t="n">
+        <v>0.4835707415079771</v>
+      </c>
+      <c r="D273" t="n">
+        <v>4.399143440066089</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0.2006732263076128</v>
+      </c>
+      <c r="F273" t="n">
+        <v>3.43205991996991</v>
+      </c>
+      <c r="G273" t="n">
+        <v>0.3009775551999549</v>
+      </c>
+      <c r="H273" t="n">
+        <v>3.828203615670223</v>
+      </c>
+      <c r="I273" t="n">
+        <v>0.111244939609878</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>3.687206638119256</v>
+      </c>
+      <c r="C274" t="n">
+        <v>0.3900915440960384</v>
+      </c>
+      <c r="D274" t="n">
+        <v>4.128747996485882</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0.3097745332385715</v>
+      </c>
+      <c r="F274" t="n">
+        <v>3.44889282701859</v>
+      </c>
+      <c r="G274" t="n">
+        <v>0.3711664048937635</v>
+      </c>
+      <c r="H274" t="n">
+        <v>3.687774208035388</v>
+      </c>
+      <c r="I274" t="n">
+        <v>0.3082990082631021</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>3.251265909861178</v>
+      </c>
+      <c r="C275" t="n">
+        <v>0.1366849347166799</v>
+      </c>
+      <c r="D275" t="n">
+        <v>4.027401561127464</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0.2956150435211136</v>
+      </c>
+      <c r="F275" t="n">
+        <v>3.02326173050993</v>
+      </c>
+      <c r="G275" t="n">
+        <v>0.05353363147448942</v>
+      </c>
+      <c r="H275" t="n">
+        <v>3.474062854979176</v>
+      </c>
+      <c r="I275" t="n">
+        <v>0.1524263272751458</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2023-11-01</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>3.133346274591187</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0.1468982372211602</v>
+      </c>
+      <c r="D276" t="n">
+        <v>4.017980521102138</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0.3002019540418122</v>
+      </c>
+      <c r="F276" t="n">
+        <v>2.765089998646619</v>
+      </c>
+      <c r="G276" t="n">
+        <v>0.007408382996931806</v>
+      </c>
+      <c r="H276" t="n">
+        <v>3.290743871150426</v>
+      </c>
+      <c r="I276" t="n">
+        <v>0.1106111891950201</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>3.315909942710293</v>
+      </c>
+      <c r="C277" t="n">
+        <v>0.1924399963653789</v>
+      </c>
+      <c r="D277" t="n">
+        <v>3.915472769862705</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0.2570488360777556</v>
+      </c>
+      <c r="F277" t="n">
+        <v>2.767265846736033</v>
+      </c>
+      <c r="G277" t="n">
+        <v>0.1374564789740962</v>
+      </c>
+      <c r="H277" t="n">
+        <v>3.1123879882345</v>
+      </c>
+      <c r="I277" t="n">
+        <v>0.1811022313788824</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>3.08834298648557</v>
+      </c>
+      <c r="C278" t="n">
+        <v>0.3099685496905202</v>
+      </c>
+      <c r="D278" t="n">
+        <v>3.858354094937266</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0.3588818467727739</v>
+      </c>
+      <c r="F278" t="n">
+        <v>2.698751449360604</v>
+      </c>
+      <c r="G278" t="n">
+        <v>0.4685188229492043</v>
+      </c>
+      <c r="H278" t="n">
+        <v>3.159014510020852</v>
+      </c>
+      <c r="I278" t="n">
+        <v>0.5182765025872449</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>3.157074141648697</v>
+      </c>
+      <c r="C279" t="n">
+        <v>0.4097540184308635</v>
+      </c>
+      <c r="D279" t="n">
+        <v>3.761964731375134</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0.3960944136371047</v>
+      </c>
+      <c r="F279" t="n">
+        <v>2.705057426970159</v>
+      </c>
+      <c r="G279" t="n">
+        <v>0.3010717499795534</v>
+      </c>
+      <c r="H279" t="n">
+        <v>3.059467984974007</v>
+      </c>
+      <c r="I279" t="n">
+        <v>0.2639893744276867</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>3.486834912083658</v>
+      </c>
+      <c r="C280" t="n">
+        <v>0.4431338373525273</v>
+      </c>
+      <c r="D280" t="n">
+        <v>3.816193506736099</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0.3891445158509699</v>
+      </c>
+      <c r="F280" t="n">
+        <v>2.927939232712617</v>
+      </c>
+      <c r="G280" t="n">
+        <v>0.3588965562244084</v>
+      </c>
+      <c r="H280" t="n">
+        <v>3.122173857921662</v>
+      </c>
+      <c r="I280" t="n">
+        <v>0.3883591005208187</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>3.360795126219673</v>
+      </c>
+      <c r="C281" t="n">
+        <v>0.2170676655621095</v>
+      </c>
+      <c r="D281" t="n">
+        <v>3.626025171759095</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0.2705245081946694</v>
+      </c>
+      <c r="F281" t="n">
+        <v>2.826154012888593</v>
+      </c>
+      <c r="G281" t="n">
+        <v>0.2462653814268689</v>
+      </c>
+      <c r="H281" t="n">
+        <v>3.006720905553606</v>
+      </c>
+      <c r="I281" t="n">
+        <v>0.2417854420575516</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>3.244278584003113</v>
+      </c>
+      <c r="C282" t="n">
+        <v>0.04855873210594108</v>
+      </c>
+      <c r="D282" t="n">
+        <v>3.394419668976645</v>
+      </c>
+      <c r="E282" t="n">
+        <v>0.1404065493674</v>
+      </c>
+      <c r="F282" t="n">
+        <v>2.661672908863921</v>
+      </c>
+      <c r="G282" t="n">
+        <v>0.005675322885334566</v>
+      </c>
+      <c r="H282" t="n">
+        <v>2.771176406372033</v>
+      </c>
+      <c r="I282" t="n">
+        <v>0.06459314495028678</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>2.970257948647093</v>
+      </c>
+      <c r="C283" t="n">
+        <v>-0.04182964796041189</v>
+      </c>
+      <c r="D283" t="n">
+        <v>3.265417323447561</v>
+      </c>
+      <c r="E283" t="n">
+        <v>0.09273959037392476</v>
+      </c>
+      <c r="F283" t="n">
+        <v>2.548373440470164</v>
+      </c>
+      <c r="G283" t="n">
+        <v>0.1548464506923475</v>
+      </c>
+      <c r="H283" t="n">
+        <v>2.753161906357326</v>
+      </c>
+      <c r="I283" t="n">
+        <v>0.2402294436318897</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>2.941475793558301</v>
+      </c>
+      <c r="C284" t="n">
+        <v>0.1677080538199149</v>
+      </c>
+      <c r="D284" t="n">
+        <v>3.230191610564481</v>
+      </c>
+      <c r="E284" t="n">
+        <v>0.1727441188479562</v>
+      </c>
+      <c r="F284" t="n">
+        <v>2.594376777467322</v>
+      </c>
+      <c r="G284" t="n">
+        <v>0.1594638130469006</v>
+      </c>
+      <c r="H284" t="n">
+        <v>2.806216333768274</v>
+      </c>
+      <c r="I284" t="n">
+        <v>0.190744801389009</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>2.607144490692037</v>
+      </c>
+      <c r="C285" t="n">
+        <v>0.1572221743858515</v>
+      </c>
+      <c r="D285" t="n">
+        <v>3.285095936430005</v>
+      </c>
+      <c r="E285" t="n">
+        <v>0.2539662632470074</v>
+      </c>
+      <c r="F285" t="n">
+        <v>2.412994957427461</v>
+      </c>
+      <c r="G285" t="n">
+        <v>0.1236503523630805</v>
+      </c>
+      <c r="H285" t="n">
+        <v>2.873279917118543</v>
+      </c>
+      <c r="I285" t="n">
+        <v>0.1765505121592126</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>2.426483031541671</v>
+      </c>
+      <c r="C286" t="n">
+        <v>0.2133336729690294</v>
+      </c>
+      <c r="D286" t="n">
+        <v>3.282357449466899</v>
+      </c>
+      <c r="E286" t="n">
+        <v>0.3071149335418299</v>
+      </c>
+      <c r="F286" t="n">
+        <v>2.260766436883843</v>
+      </c>
+      <c r="G286" t="n">
+        <v>0.2219728950915822</v>
+      </c>
+      <c r="H286" t="n">
+        <v>2.838627996468368</v>
+      </c>
+      <c r="I286" t="n">
+        <v>0.2745110779026616</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>2.578844053871343</v>
+      </c>
+      <c r="C287" t="n">
+        <v>0.2856398459641696</v>
+      </c>
+      <c r="D287" t="n">
+        <v>3.298689706765301</v>
+      </c>
+      <c r="E287" t="n">
+        <v>0.3114750009353573</v>
+      </c>
+      <c r="F287" t="n">
+        <v>2.477692535642562</v>
+      </c>
+      <c r="G287" t="n">
+        <v>0.2657775200541224</v>
+      </c>
+      <c r="H287" t="n">
+        <v>2.986502108265898</v>
+      </c>
+      <c r="I287" t="n">
+        <v>0.2964378857337246</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>2.719472461284833</v>
+      </c>
+      <c r="C288" t="n">
+        <v>0.2841926173284826</v>
+      </c>
+      <c r="D288" t="n">
+        <v>3.285935619350044</v>
+      </c>
+      <c r="E288" t="n">
+        <v>0.2878180840515832</v>
+      </c>
+      <c r="F288" t="n">
+        <v>2.5878034125423</v>
+      </c>
+      <c r="G288" t="n">
+        <v>0.1148649734123763</v>
+      </c>
+      <c r="H288" t="n">
+        <v>2.980710120125618</v>
+      </c>
+      <c r="I288" t="n">
+        <v>0.1049809419213288</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>2.870690967509981</v>
+      </c>
+      <c r="C289" t="n">
+        <v>0.3399383308901438</v>
+      </c>
+      <c r="D289" t="n">
+        <v>3.213333546193264</v>
+      </c>
+      <c r="E289" t="n">
+        <v>0.186575837499281</v>
+      </c>
+      <c r="F289" t="n">
+        <v>2.728094690120009</v>
+      </c>
+      <c r="G289" t="n">
+        <v>0.2743968484478998</v>
+      </c>
+      <c r="H289" t="n">
+        <v>2.988589624519045</v>
+      </c>
+      <c r="I289" t="n">
+        <v>0.1887675255320076</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>2.990978307899961</v>
+      </c>
+      <c r="C290" t="n">
+        <v>0.4272616213901737</v>
+      </c>
+      <c r="D290" t="n">
+        <v>3.282970485398584</v>
+      </c>
+      <c r="E290" t="n">
+        <v>0.4265929177532435</v>
+      </c>
+      <c r="F290" t="n">
+        <v>2.607379530393517</v>
+      </c>
+      <c r="G290" t="n">
+        <v>0.350458877091353</v>
+      </c>
+      <c r="H290" t="n">
+        <v>2.780138099441509</v>
+      </c>
+      <c r="I290" t="n">
+        <v>0.3148249541047976</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>2.801583447761335</v>
+      </c>
+      <c r="C291" t="n">
+        <v>0.2251058906888259</v>
+      </c>
+      <c r="D291" t="n">
+        <v>3.13755688228059</v>
+      </c>
+      <c r="E291" t="n">
+        <v>0.2547452855180321</v>
+      </c>
+      <c r="F291" t="n">
+        <v>2.710484673485714</v>
+      </c>
+      <c r="G291" t="n">
+        <v>0.4018593970514406</v>
+      </c>
+      <c r="H291" t="n">
+        <v>2.968643293811746</v>
+      </c>
+      <c r="I291" t="n">
+        <v>0.4478797948421542</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>2.381981462805549</v>
+      </c>
+      <c r="C292" t="n">
+        <v>0.03315826188146076</v>
+      </c>
+      <c r="D292" t="n">
+        <v>2.808783050077035</v>
+      </c>
+      <c r="E292" t="n">
+        <v>0.06913185749619633</v>
+      </c>
+      <c r="F292" t="n">
+        <v>2.359433670898436</v>
+      </c>
+      <c r="G292" t="n">
+        <v>0.01588297424575114</v>
+      </c>
+      <c r="H292" t="n">
+        <v>2.670294814316976</v>
+      </c>
+      <c r="I292" t="n">
+        <v>0.09748691517839081</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>2.32538823025783</v>
+      </c>
+      <c r="C293" t="n">
+        <v>0.1616711227856227</v>
+      </c>
+      <c r="D293" t="n">
+        <v>2.776020072469931</v>
+      </c>
+      <c r="E293" t="n">
+        <v>0.2385704197242822</v>
+      </c>
+      <c r="F293" t="n">
+        <v>2.277425997843396</v>
+      </c>
+      <c r="G293" t="n">
+        <v>0.1659507229575752</v>
+      </c>
+      <c r="H293" t="n">
+        <v>2.614795918367352</v>
+      </c>
+      <c r="I293" t="n">
+        <v>0.1875992879210031</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>2.377265107368087</v>
+      </c>
+      <c r="C294" t="n">
+        <v>0.09928130327003792</v>
+      </c>
+      <c r="D294" t="n">
+        <v>2.765840393593089</v>
+      </c>
+      <c r="E294" t="n">
+        <v>0.1304879206780463</v>
+      </c>
+      <c r="F294" t="n">
+        <v>2.458086065440868</v>
+      </c>
+      <c r="G294" t="n">
+        <v>0.1823226317875459</v>
+      </c>
+      <c r="H294" t="n">
+        <v>2.783883382495933</v>
+      </c>
+      <c r="I294" t="n">
+        <v>0.2294784146866347</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>2.680453865910226</v>
+      </c>
+      <c r="C295" t="n">
+        <v>0.2541949971929469</v>
+      </c>
+      <c r="D295" t="n">
+        <v>2.910895442696071</v>
+      </c>
+      <c r="E295" t="n">
+        <v>0.2340215299807769</v>
+      </c>
+      <c r="F295" t="n">
+        <v>2.593512979706802</v>
+      </c>
+      <c r="G295" t="n">
+        <v>0.2872289919291005</v>
+      </c>
+      <c r="H295" t="n">
+        <v>2.8073722050588</v>
+      </c>
+      <c r="I295" t="n">
+        <v>0.2631369743222756</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>2.742618052167134</v>
+      </c>
+      <c r="C296" t="n">
+        <v>0.2283509885357748</v>
+      </c>
+      <c r="D296" t="n">
+        <v>3.05449300808931</v>
+      </c>
+      <c r="E296" t="n">
+        <v>0.3125209822436803</v>
+      </c>
+      <c r="F296" t="n">
+        <v>2.605547294239341</v>
+      </c>
+      <c r="G296" t="n">
+        <v>0.1712126113473822</v>
+      </c>
+      <c r="H296" t="n">
+        <v>2.86304724556794</v>
+      </c>
+      <c r="I296" t="n">
+        <v>0.2450028147572558</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>2.938591743031616</v>
+      </c>
+      <c r="C297" t="n">
+        <v>0.3482644202266627</v>
+      </c>
+      <c r="D297" t="n">
+        <v>3.111806098514469</v>
+      </c>
+      <c r="E297" t="n">
+        <v>0.3097218588179462</v>
+      </c>
+      <c r="F297" t="n">
+        <v>2.7476208541517</v>
+      </c>
+      <c r="G297" t="n">
+        <v>0.2622873345935917</v>
+      </c>
+      <c r="H297" t="n">
+        <v>2.912416347215907</v>
+      </c>
+      <c r="I297" t="n">
+        <v>0.2246302301668779</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>3.022571584713329</v>
+      </c>
+      <c r="C298" t="n">
+        <v>0.2950901819104068</v>
+      </c>
+      <c r="D298" t="n">
+        <v>3.019966825885789</v>
+      </c>
+      <c r="E298" t="n">
+        <v>0.2177737336973129</v>
+      </c>
+      <c r="F298" t="n">
+        <v>2.787442414870656</v>
+      </c>
+      <c r="G298" t="n">
+        <v>0.2608155986582039</v>
+      </c>
+      <c r="H298" t="n">
+        <v>2.825069249833967</v>
+      </c>
+      <c r="I298" t="n">
+        <v>0.1894029073346237</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr"/>
+      <c r="C299" t="inlineStr"/>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="n">
+        <v>2.712580525969122</v>
+      </c>
+      <c r="G299" t="n">
+        <v>0.1927522037218354</v>
+      </c>
+      <c r="H299" t="n">
+        <v>2.75453840687383</v>
+      </c>
+      <c r="I299" t="n">
+        <v>0.2276415079477623</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>2.988299628363511</v>
+      </c>
+      <c r="C300" t="n">
+        <v>0.2522783697512576</v>
+      </c>
+      <c r="D300" t="n">
+        <v>2.894343411110523</v>
+      </c>
+      <c r="E300" t="n">
+        <v>0.1891543438916843</v>
+      </c>
+      <c r="F300" t="n">
+        <v>2.820189831269992</v>
+      </c>
+      <c r="G300" t="n">
+        <v>0.219752719537647</v>
+      </c>
+      <c r="H300" t="n">
+        <v>2.829092786499077</v>
+      </c>
+      <c r="I300" t="n">
+        <v>0.1776129138734595</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>3.00226204316838</v>
+      </c>
+      <c r="C301" t="n">
+        <v>0.297788428704604</v>
+      </c>
+      <c r="D301" t="n">
+        <v>2.837998245815232</v>
+      </c>
+      <c r="E301" t="n">
+        <v>0.2329002576704653</v>
+      </c>
+      <c r="F301" t="n">
+        <v>2.878083518031027</v>
+      </c>
+      <c r="G301" t="n">
+        <v>0.3308571071852118</v>
+      </c>
+      <c r="H301" t="n">
+        <v>2.971110180682146</v>
+      </c>
+      <c r="I301" t="n">
+        <v>0.3271383630529812</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>2.8286797395499</v>
+      </c>
+      <c r="C302" t="n">
+        <v>0.170842649932057</v>
+      </c>
+      <c r="D302" t="n">
+        <v>2.949337837461607</v>
+      </c>
+      <c r="E302" t="n">
+        <v>0.2950448142634121</v>
+      </c>
+      <c r="F302" t="n">
+        <v>2.875208305094201</v>
+      </c>
+      <c r="G302" t="n">
+        <v>0.3476543056246895</v>
+      </c>
+      <c r="H302" t="n">
+        <v>3.104657789335974</v>
+      </c>
+      <c r="I302" t="n">
+        <v>0.444927513566773</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>2.664589087694091</v>
+      </c>
+      <c r="C303" t="n">
+        <v>0.267003074209704</v>
+      </c>
+      <c r="D303" t="n">
+        <v>2.733506243877803</v>
+      </c>
+      <c r="E303" t="n">
+        <v>0.2160502174024082</v>
+      </c>
+      <c r="F303" t="n">
+        <v>2.873230041057484</v>
+      </c>
+      <c r="G303" t="n">
+        <v>0.3999286948838554</v>
+      </c>
+      <c r="H303" t="n">
+        <v>3.049262855088108</v>
+      </c>
+      <c r="I303" t="n">
+        <v>0.3939122649955218</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>3.320205581223679</v>
+      </c>
+      <c r="C304" t="n">
+        <v>0.8651438343614481</v>
+      </c>
+      <c r="D304" t="n">
+        <v>2.673098489852999</v>
+      </c>
+      <c r="E304" t="n">
+        <v>0.1957950538511444</v>
+      </c>
+      <c r="F304" t="n">
+        <v>3.542928831754533</v>
+      </c>
+      <c r="G304" t="n">
+        <v>0.6669806004369283</v>
+      </c>
+      <c r="H304" t="n">
+        <v>3.253849776876594</v>
+      </c>
+      <c r="I304" t="n">
+        <v>0.2962135839517099</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>3.947026908704276</v>
+      </c>
+      <c r="C305" t="n">
+        <v>0.6400377846336402</v>
+      </c>
+      <c r="D305" t="n">
+        <v>2.988424575516602</v>
+      </c>
+      <c r="E305" t="n">
+        <v>0.376460730477457</v>
+      </c>
+      <c r="F305" t="n">
+        <v>3.80182322631788</v>
+      </c>
+      <c r="G305" t="n">
+        <v>0.4164014631565349</v>
+      </c>
+      <c r="H305" t="n">
+        <v>3.329827413108966</v>
+      </c>
+      <c r="I305" t="n">
+        <v>0.2613206744856766</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>4.270032656680245</v>
+      </c>
+      <c r="C306" t="n">
+        <v>0.4729142286413968</v>
+      </c>
+      <c r="D306" t="n">
+        <v>2.957113582689819</v>
+      </c>
+      <c r="E306" t="n">
+        <v>0.2080954496262777</v>
+      </c>
+      <c r="F306" t="n">
+        <v>4.111410033233098</v>
+      </c>
+      <c r="G306" t="n">
+        <v>0.4811143524811712</v>
+      </c>
+      <c r="H306" t="n">
+        <v>3.463709356864597</v>
+      </c>
+      <c r="I306" t="n">
+        <v>0.3593433116647615</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>3.72652984841868</v>
+      </c>
+      <c r="C307" t="n">
+        <v>-0.4224816530380648</v>
+      </c>
+      <c r="D307" t="n">
+        <v>2.80581107579545</v>
+      </c>
+      <c r="E307" t="n">
+        <v>-0.01666066684318235</v>
+      </c>
+      <c r="F307" t="n">
+        <v>3.71697056247684</v>
+      </c>
+      <c r="G307" t="n">
+        <v>-0.09272207697451629</v>
+      </c>
+      <c r="H307" t="n">
+        <v>3.343614465473621</v>
+      </c>
+      <c r="I307" t="n">
+        <v>0.1467571284778035</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>3.539751427193671</v>
+      </c>
+      <c r="C308" t="n">
+        <v>0.07366914435544825</v>
+      </c>
+      <c r="D308" t="n">
+        <v>2.786747157096725</v>
+      </c>
+      <c r="E308" t="n">
+        <v>0.2154345141564873</v>
+      </c>
+      <c r="F308" t="n">
+        <v>3.701165721487087</v>
+      </c>
+      <c r="G308" t="n">
+        <v>0.155948088304636</v>
+      </c>
+      <c r="H308" t="n">
+        <v>3.344143004033828</v>
+      </c>
+      <c r="I308" t="n">
+        <v>0.2455155058386671</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -578,6 +578,88 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>09/04</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>09/08</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>09/08</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -660,6 +660,88 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>09/08</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>09/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>09/09</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -742,6 +742,88 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>09/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>09/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>09/10</t>
         </is>
       </c>
     </row>
